--- a/fares.xlsx
+++ b/fares.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="All fares" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Slot view" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tracked flights" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25760,12 +25760,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -25792,7 +25792,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>slot</t>
+          <t>row</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -25929,31 +25929,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AI 2803</t>
+          <t>AI 427</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>13670</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="5">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -25998,7 +25998,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>10226</v>
+        <v>10121</v>
       </c>
     </row>
     <row r="6">
@@ -26019,31 +26019,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AI 427</t>
+          <t>AI 2487</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>10121</v>
+        <v>15376</v>
       </c>
     </row>
     <row r="7">
@@ -26064,31 +26064,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AI 427</t>
+          <t>AI 2487</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>12867</v>
+        <v>10226</v>
       </c>
     </row>
     <row r="8">
@@ -26104,12 +26104,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Early morning</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -26124,16 +26124,16 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AI 2487</t>
+          <t>6E 810</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>15376</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="9">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Early morning</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -26169,16 +26169,16 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>AI 2487</t>
+          <t>6E 810</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>10226</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="10">
@@ -26194,36 +26194,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>AI 2487</t>
+          <t>6E 826</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>11433</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="11">
@@ -26244,31 +26244,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6E 810</t>
+          <t>6E 826</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>10096</v>
+        <v>9795</v>
       </c>
     </row>
     <row r="12">
@@ -26289,31 +26289,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6E 810</t>
+          <t>6E 811</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>10096</v>
+        <v>11603</v>
       </c>
     </row>
     <row r="13">
@@ -26334,31 +26334,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6E 810</t>
+          <t>6E 811</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>13365</v>
+        <v>10096</v>
       </c>
     </row>
     <row r="14">
@@ -26369,17 +26369,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -26394,16 +26394,16 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6E 826</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>10096</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="15">
@@ -26414,17 +26414,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -26439,16 +26439,16 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6E 826</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>9795</v>
+        <v>4533</v>
       </c>
     </row>
     <row r="16">
@@ -26459,41 +26459,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>AI 429</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6E 826</t>
+          <t>AI 429</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>12160</v>
+        <v>13489</v>
       </c>
     </row>
     <row r="17">
@@ -26504,17 +26504,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>9I 843</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -26529,16 +26529,13 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6E 811</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>11603</v>
+          <t>9I 843</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -26549,17 +26546,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>9I 843</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -26574,16 +26571,13 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6E 811</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>10096</v>
+          <t>9I 843</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -26594,7 +26588,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Delhi → Bengaluru</t>
+          <t>Delhi → Jaipur</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -26604,31 +26598,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6E 811</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>11075</v>
+        <v>3220</v>
       </c>
     </row>
     <row r="20">
@@ -26644,36 +26638,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>AI 1767</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4533</v>
+        <v>4795</v>
       </c>
     </row>
     <row r="21">
@@ -26689,36 +26683,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>AI 1767</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4533</v>
+        <v>5320</v>
       </c>
     </row>
     <row r="22">
@@ -26734,36 +26728,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>AI 1767</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4533</v>
+        <v>3010</v>
       </c>
     </row>
     <row r="23">
@@ -26779,36 +26773,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>AI 429</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>13489</v>
+        <v>5845</v>
       </c>
     </row>
     <row r="24">
@@ -26829,27 +26823,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -26864,12 +26858,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Delhi → Jaipur</t>
+          <t>Delhi → Mumbai</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -26879,26 +26873,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>AI 2975</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4795</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="26">
@@ -26909,41 +26903,41 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Delhi → Jaipur</t>
+          <t>Delhi → Mumbai</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Early morning</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>AI 2975</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3220</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="27">
@@ -26954,12 +26948,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Delhi → Jaipur</t>
+          <t>Delhi → Mumbai</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -26969,26 +26963,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>AI 2963</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4795</v>
+        <v>7433</v>
       </c>
     </row>
     <row r="28">
@@ -26999,41 +26993,41 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Delhi → Jaipur</t>
+          <t>Delhi → Mumbai</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>Morning</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6E 6131</t>
+          <t>AI 2963</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>5845</v>
+        <v>7170</v>
       </c>
     </row>
     <row r="29">
@@ -27044,12 +27038,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Delhi → Jaipur</t>
+          <t>Delhi → Mumbai</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -27059,26 +27053,26 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>6E 6131</t>
+          <t>AI 2955</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3220</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="30">
@@ -27099,27 +27093,27 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>AI 2975</t>
+          <t>AI 2441</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -27139,7 +27133,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -27149,26 +27143,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>AI 2975</t>
+          <t>6E 6218</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>7433</v>
+        <v>7225</v>
       </c>
     </row>
     <row r="32">
@@ -27184,7 +27178,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -27194,26 +27188,26 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>AI 2975</t>
+          <t>6E 6218</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>7170</v>
+        <v>6963</v>
       </c>
     </row>
     <row r="33">
@@ -27229,7 +27223,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -27249,16 +27243,16 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>AI 2963</t>
+          <t>6E 675</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>7433</v>
+        <v>7225</v>
       </c>
     </row>
     <row r="34">
@@ -27274,7 +27268,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -27294,16 +27288,16 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>AI 2963</t>
+          <t>6E 675</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>7170</v>
+        <v>6963</v>
       </c>
     </row>
     <row r="35">
@@ -27319,36 +27313,36 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>Evening</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>AI 2963</t>
+          <t>6E 329</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>7170</v>
+        <v>7593</v>
       </c>
     </row>
     <row r="36">
@@ -27364,7 +27358,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -27374,12 +27368,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -27389,11 +27383,11 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>AI 2955</t>
+          <t>6E 329</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>8000</v>
+        <v>7225</v>
       </c>
     </row>
     <row r="37">
@@ -27404,41 +27398,41 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>AI 2441</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7170</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="38">
@@ -27449,41 +27443,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>AI 2955</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>7170</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="39">
@@ -27494,41 +27488,41 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>6E 6218</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7225</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="40">
@@ -27539,41 +27533,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>05:40</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>6E 6218</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>6963</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="41">
@@ -27584,41 +27578,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6E 6218</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>6963</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="42">
@@ -27629,41 +27623,41 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>6E 675</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7225</v>
+        <v>5536</v>
       </c>
     </row>
     <row r="43">
@@ -27674,17 +27668,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -27699,16 +27693,16 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>6E 675</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>6963</v>
+        <v>7555</v>
       </c>
     </row>
     <row r="44">
@@ -27719,41 +27713,41 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Morning</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>6E 675</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>6963</v>
+        <v>8047</v>
       </c>
     </row>
     <row r="45">
@@ -27764,17 +27758,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -27789,16 +27783,16 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>6E 329</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>7593</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="46">
@@ -27809,17 +27803,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -27834,16 +27828,16 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6E 329</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7225</v>
+        <v>6072</v>
       </c>
     </row>
     <row r="47">
@@ -27854,41 +27848,41 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Delhi → Mumbai</t>
+          <t>Pune → Bengaluru</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>D+1</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6E 329</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>6963</v>
+        <v>5613</v>
       </c>
     </row>
     <row r="48">
@@ -27904,36 +27898,36 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6E 391</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5313</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="49">
@@ -27949,36 +27943,36 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Early morning</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6E 391</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5313</v>
+        <v>7143</v>
       </c>
     </row>
     <row r="50">
@@ -27994,36 +27988,36 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Evening</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6E 174</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>5313</v>
+        <v>5252</v>
       </c>
     </row>
     <row r="51">
@@ -28039,35 +28033,1070 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>QP 1326</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>QP 1326</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>5613</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>QP 1326</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>QP 1326</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>5083</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>QP 1316</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>QP 1316</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>9202</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>QP 1316</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>QP 1316</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>5613</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>QP 1318</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>QP 1318</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>7671</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>QP 1318</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>QP 1318</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>5252</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
           <t>IndiGo</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Evening</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6E 361</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>6E 361</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>6E 361</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>+3wk</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>6E 361</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>6E 6564</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>6E 6564</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>6E 6564</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>6E 6564</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>6E 6877</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>6E 6877</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>6E 6877</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>6E 6877</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>6E 391</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>6E 391</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>6E 391</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>6E 391</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>6E 302</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>6E 302</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>6E 302</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>6E 302</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>6094</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>6E 137</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>6E 137</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>6E 137</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>6E 137</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>6E 174</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>17:40</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>6E 174</t>
         </is>
       </c>
-      <c r="I51" t="n">
+      <c r="I69" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>6E 174</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>6E 174</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>6E 107</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>6E 107</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>6E 107</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>6E 107</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>6094</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>6E 6055</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>+1wk</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>6E 6055</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>5313</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Pune → Bengaluru</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>IndiGo</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>6E 6055</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>23:50</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>6E 6055</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
         <v>5313</v>
       </c>
     </row>

--- a/fares.xlsx
+++ b/fares.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P834"/>
+  <dimension ref="A1:P835"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -45354,7 +45354,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>2026-07-26T11:18:02</t>
+          <t>2026-07-26T07:11:54</t>
         </is>
       </c>
       <c r="B592" t="inlineStr">
@@ -45389,32 +45389,32 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
         <is>
-          <t>6E 850</t>
+          <t>AI 2485</t>
         </is>
       </c>
       <c r="J592" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="K592" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="L592" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="M592" t="n">
         <v>0</v>
       </c>
       <c r="N592" t="n">
-        <v>12747</v>
+        <v>18888</v>
       </c>
       <c r="O592" t="inlineStr">
         <is>
@@ -45465,32 +45465,32 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
         <is>
-          <t>AI 2417</t>
+          <t>6E 850</t>
         </is>
       </c>
       <c r="J593" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="K593" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="L593" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="M593" t="n">
         <v>0</v>
       </c>
       <c r="N593" t="n">
-        <v>19219</v>
+        <v>12747</v>
       </c>
       <c r="O593" t="inlineStr">
         <is>
@@ -45541,22 +45541,22 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
         <is>
-          <t>6E 176</t>
+          <t>AI 2417</t>
         </is>
       </c>
       <c r="J594" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K594" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="L594" t="n">
@@ -45566,7 +45566,7 @@
         <v>0</v>
       </c>
       <c r="N594" t="n">
-        <v>13365</v>
+        <v>19219</v>
       </c>
       <c r="O594" t="inlineStr">
         <is>
@@ -45622,17 +45622,17 @@
       </c>
       <c r="I595" t="inlineStr">
         <is>
-          <t>6E 828</t>
+          <t>6E 176</t>
         </is>
       </c>
       <c r="J595" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="K595" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="L595" t="n">
@@ -45642,7 +45642,7 @@
         <v>0</v>
       </c>
       <c r="N595" t="n">
-        <v>12160</v>
+        <v>13365</v>
       </c>
       <c r="O595" t="inlineStr">
         <is>
@@ -45693,22 +45693,22 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
         <is>
-          <t>AI 2819</t>
+          <t>6E 828</t>
         </is>
       </c>
       <c r="J596" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="K596" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="L596" t="n">
@@ -45718,7 +45718,7 @@
         <v>0</v>
       </c>
       <c r="N596" t="n">
-        <v>16358</v>
+        <v>12160</v>
       </c>
       <c r="O596" t="inlineStr">
         <is>
@@ -45769,22 +45769,22 @@
       </c>
       <c r="H597" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I597" t="inlineStr">
         <is>
-          <t>6E 880</t>
+          <t>AI 2819</t>
         </is>
       </c>
       <c r="J597" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="K597" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="L597" t="n">
@@ -45794,7 +45794,7 @@
         <v>0</v>
       </c>
       <c r="N597" t="n">
-        <v>12747</v>
+        <v>16358</v>
       </c>
       <c r="O597" t="inlineStr">
         <is>
@@ -45845,22 +45845,22 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
         <is>
-          <t>AI 2797</t>
+          <t>6E 880</t>
         </is>
       </c>
       <c r="J598" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="K598" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="L598" t="n">
@@ -45870,7 +45870,7 @@
         <v>0</v>
       </c>
       <c r="N598" t="n">
-        <v>15376</v>
+        <v>12747</v>
       </c>
       <c r="O598" t="inlineStr">
         <is>
@@ -45921,32 +45921,32 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
         <is>
-          <t>QP 1822</t>
+          <t>AI 2797</t>
         </is>
       </c>
       <c r="J599" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K599" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="L599" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M599" t="n">
         <v>0</v>
       </c>
       <c r="N599" t="n">
-        <v>13042</v>
+        <v>15376</v>
       </c>
       <c r="O599" t="inlineStr">
         <is>
@@ -45997,32 +45997,32 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
         <is>
-          <t>6E 837</t>
+          <t>QP 1822</t>
         </is>
       </c>
       <c r="J600" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="K600" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="L600" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M600" t="n">
         <v>0</v>
       </c>
       <c r="N600" t="n">
-        <v>12747</v>
+        <v>13042</v>
       </c>
       <c r="O600" t="inlineStr">
         <is>
@@ -46073,22 +46073,22 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>AI 2420</t>
+          <t>6E 837</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K601" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="L601" t="n">
@@ -46098,7 +46098,7 @@
         <v>0</v>
       </c>
       <c r="N601" t="n">
-        <v>13670</v>
+        <v>12747</v>
       </c>
       <c r="O601" t="inlineStr">
         <is>
@@ -46149,32 +46149,32 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
         <is>
-          <t>6E 811</t>
+          <t>AI 2420</t>
         </is>
       </c>
       <c r="J602" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="K602" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="L602" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M602" t="n">
         <v>0</v>
       </c>
       <c r="N602" t="n">
-        <v>11603</v>
+        <v>13670</v>
       </c>
       <c r="O602" t="inlineStr">
         <is>
@@ -46225,32 +46225,32 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
         <is>
-          <t>AI 2487</t>
+          <t>6E 811</t>
         </is>
       </c>
       <c r="J603" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="K603" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="L603" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M603" t="n">
         <v>0</v>
       </c>
       <c r="N603" t="n">
-        <v>16080</v>
+        <v>11603</v>
       </c>
       <c r="O603" t="inlineStr">
         <is>
@@ -46301,22 +46301,22 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
         <is>
-          <t>IX 1070</t>
+          <t>AI 2487</t>
         </is>
       </c>
       <c r="J604" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K604" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="L604" t="n">
@@ -46326,7 +46326,7 @@
         <v>0</v>
       </c>
       <c r="N604" t="n">
-        <v>11440</v>
+        <v>16080</v>
       </c>
       <c r="O604" t="inlineStr">
         <is>
@@ -46377,22 +46377,22 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
         <is>
-          <t>AI 2512</t>
+          <t>IX 1070</t>
         </is>
       </c>
       <c r="J605" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K605" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="L605" t="n">
@@ -46402,7 +46402,7 @@
         <v>0</v>
       </c>
       <c r="N605" t="n">
-        <v>12489</v>
+        <v>11440</v>
       </c>
       <c r="O605" t="inlineStr">
         <is>
@@ -46458,27 +46458,27 @@
       </c>
       <c r="I606" t="inlineStr">
         <is>
-          <t>AI 2809</t>
+          <t>AI 2512</t>
         </is>
       </c>
       <c r="J606" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K606" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="L606" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M606" t="n">
         <v>0</v>
       </c>
       <c r="N606" t="n">
-        <v>12982</v>
+        <v>12489</v>
       </c>
       <c r="O606" t="inlineStr">
         <is>
@@ -46529,12 +46529,12 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
         <is>
-          <t>6E 861</t>
+          <t>AI 2809</t>
         </is>
       </c>
       <c r="J607" t="inlineStr">
@@ -46544,17 +46544,17 @@
       </c>
       <c r="K607" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="L607" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M607" t="n">
         <v>0</v>
       </c>
       <c r="N607" t="n">
-        <v>11075</v>
+        <v>12982</v>
       </c>
       <c r="O607" t="inlineStr">
         <is>
@@ -46605,22 +46605,22 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
         <is>
-          <t>AI 2807</t>
+          <t>6E 861</t>
         </is>
       </c>
       <c r="J608" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K608" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="L608" t="n">
@@ -46630,7 +46630,7 @@
         <v>0</v>
       </c>
       <c r="N608" t="n">
-        <v>8864</v>
+        <v>11075</v>
       </c>
       <c r="O608" t="inlineStr">
         <is>
@@ -46681,32 +46681,32 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
         <is>
-          <t>QP 1824</t>
+          <t>AI 2807</t>
         </is>
       </c>
       <c r="J609" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K609" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="L609" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M609" t="n">
         <v>0</v>
       </c>
       <c r="N609" t="n">
-        <v>10896</v>
+        <v>8864</v>
       </c>
       <c r="O609" t="inlineStr">
         <is>
@@ -46757,32 +46757,32 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
         <is>
-          <t>6E 6515</t>
+          <t>QP 1824</t>
         </is>
       </c>
       <c r="J610" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K610" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="L610" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M610" t="n">
         <v>0</v>
       </c>
       <c r="N610" t="n">
-        <v>10096</v>
+        <v>10896</v>
       </c>
       <c r="O610" t="inlineStr">
         <is>
@@ -46833,22 +46833,22 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
         <is>
-          <t>QP 1308</t>
+          <t>6E 6515</t>
         </is>
       </c>
       <c r="J611" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="K611" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="L611" t="n">
@@ -46858,7 +46858,7 @@
         <v>0</v>
       </c>
       <c r="N611" t="n">
-        <v>10515</v>
+        <v>10096</v>
       </c>
       <c r="O611" t="inlineStr">
         <is>
@@ -46909,22 +46909,22 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>AI 2412</t>
+          <t>QP 1308</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="K612" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="L612" t="n">
@@ -46934,7 +46934,7 @@
         <v>0</v>
       </c>
       <c r="N612" t="n">
-        <v>10908</v>
+        <v>10515</v>
       </c>
       <c r="O612" t="inlineStr">
         <is>
@@ -46985,32 +46985,32 @@
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>QP 1350</t>
+          <t>AI 2412</t>
         </is>
       </c>
       <c r="J613" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K613" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>00:25</t>
         </is>
       </c>
       <c r="L613" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M613" t="n">
         <v>0</v>
       </c>
       <c r="N613" t="n">
-        <v>10896</v>
+        <v>10908</v>
       </c>
       <c r="O613" t="inlineStr">
         <is>
@@ -47061,32 +47061,32 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
         <is>
-          <t>6E 846</t>
+          <t>QP 1350</t>
         </is>
       </c>
       <c r="J614" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="K614" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="L614" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M614" t="n">
         <v>0</v>
       </c>
       <c r="N614" t="n">
-        <v>10096</v>
+        <v>10896</v>
       </c>
       <c r="O614" t="inlineStr">
         <is>
@@ -47137,22 +47137,22 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
         <is>
-          <t>AI 2755</t>
+          <t>6E 846</t>
         </is>
       </c>
       <c r="J615" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="K615" t="inlineStr">
         <is>
-          <t>01:25</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="L615" t="n">
@@ -47162,7 +47162,7 @@
         <v>0</v>
       </c>
       <c r="N615" t="n">
-        <v>10452</v>
+        <v>10096</v>
       </c>
       <c r="O615" t="inlineStr">
         <is>
@@ -47213,22 +47213,22 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
         <is>
-          <t>QP 1812</t>
+          <t>AI 2755</t>
         </is>
       </c>
       <c r="J616" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="K616" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>01:25</t>
         </is>
       </c>
       <c r="L616" t="n">
@@ -47238,7 +47238,7 @@
         <v>0</v>
       </c>
       <c r="N616" t="n">
-        <v>10515</v>
+        <v>10452</v>
       </c>
       <c r="O616" t="inlineStr">
         <is>
@@ -47289,22 +47289,22 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
         <is>
-          <t>6E 871</t>
+          <t>QP 1812</t>
         </is>
       </c>
       <c r="J617" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="K617" t="inlineStr">
         <is>
-          <t>02:25</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="L617" t="n">
@@ -47314,7 +47314,7 @@
         <v>0</v>
       </c>
       <c r="N617" t="n">
-        <v>10096</v>
+        <v>10515</v>
       </c>
       <c r="O617" t="inlineStr">
         <is>
@@ -47355,32 +47355,32 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
         <is>
-          <t>AI 2757</t>
+          <t>6E 871</t>
         </is>
       </c>
       <c r="J618" t="inlineStr">
         <is>
-          <t>00:15</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="K618" t="inlineStr">
         <is>
-          <t>03:10</t>
+          <t>02:25</t>
         </is>
       </c>
       <c r="L618" t="n">
@@ -47390,7 +47390,7 @@
         <v>0</v>
       </c>
       <c r="N618" t="n">
-        <v>10121</v>
+        <v>10096</v>
       </c>
       <c r="O618" t="inlineStr">
         <is>
@@ -47441,22 +47441,22 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
         <is>
-          <t>6E 820</t>
+          <t>AI 2757</t>
         </is>
       </c>
       <c r="J619" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>00:15</t>
         </is>
       </c>
       <c r="K619" t="inlineStr">
         <is>
-          <t>05:55</t>
+          <t>03:10</t>
         </is>
       </c>
       <c r="L619" t="n">
@@ -47466,7 +47466,7 @@
         <v>0</v>
       </c>
       <c r="N619" t="n">
-        <v>9795</v>
+        <v>10121</v>
       </c>
       <c r="O619" t="inlineStr">
         <is>
@@ -47517,22 +47517,22 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
         <is>
-          <t>AI 2502</t>
+          <t>6E 820</t>
         </is>
       </c>
       <c r="J620" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="K620" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>05:55</t>
         </is>
       </c>
       <c r="L620" t="n">
@@ -47542,7 +47542,7 @@
         <v>0</v>
       </c>
       <c r="N620" t="n">
-        <v>10032</v>
+        <v>9795</v>
       </c>
       <c r="O620" t="inlineStr">
         <is>
@@ -47598,27 +47598,27 @@
       </c>
       <c r="I621" t="inlineStr">
         <is>
-          <t>AI 2653</t>
+          <t>AI 2502</t>
         </is>
       </c>
       <c r="J621" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="K621" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="L621" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M621" t="n">
         <v>0</v>
       </c>
       <c r="N621" t="n">
-        <v>10121</v>
+        <v>10032</v>
       </c>
       <c r="O621" t="inlineStr">
         <is>
@@ -47669,32 +47669,32 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
         <is>
-          <t>6E 2314</t>
+          <t>AI 2653</t>
         </is>
       </c>
       <c r="J622" t="inlineStr">
         <is>
-          <t>05:45</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="K622" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="L622" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M622" t="n">
         <v>0</v>
       </c>
       <c r="N622" t="n">
-        <v>9795</v>
+        <v>10121</v>
       </c>
       <c r="O622" t="inlineStr">
         <is>
@@ -47745,22 +47745,22 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
         <is>
-          <t>AI 2803</t>
+          <t>6E 2314</t>
         </is>
       </c>
       <c r="J623" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="K623" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="L623" t="n">
@@ -47770,7 +47770,7 @@
         <v>0</v>
       </c>
       <c r="N623" t="n">
-        <v>10121</v>
+        <v>9795</v>
       </c>
       <c r="O623" t="inlineStr">
         <is>
@@ -47821,22 +47821,22 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
         <is>
-          <t>6E 810</t>
+          <t>AI 2803</t>
         </is>
       </c>
       <c r="J624" t="inlineStr">
         <is>
-          <t>07:05</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="K624" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="L624" t="n">
@@ -47846,7 +47846,7 @@
         <v>0</v>
       </c>
       <c r="N624" t="n">
-        <v>9795</v>
+        <v>10121</v>
       </c>
       <c r="O624" t="inlineStr">
         <is>
@@ -47902,21 +47902,21 @@
       </c>
       <c r="I625" t="inlineStr">
         <is>
-          <t>6E 873</t>
+          <t>6E 810</t>
         </is>
       </c>
       <c r="J625" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="K625" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="L625" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M625" t="n">
         <v>0</v>
@@ -47973,22 +47973,22 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
         <is>
-          <t>AI 427</t>
+          <t>6E 873</t>
         </is>
       </c>
       <c r="J626" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="K626" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="L626" t="n">
@@ -47998,7 +47998,7 @@
         <v>0</v>
       </c>
       <c r="N626" t="n">
-        <v>10121</v>
+        <v>9795</v>
       </c>
       <c r="O626" t="inlineStr">
         <is>
@@ -48049,12 +48049,12 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
         <is>
-          <t>IX 1482</t>
+          <t>AI 427</t>
         </is>
       </c>
       <c r="J627" t="inlineStr">
@@ -48064,17 +48064,17 @@
       </c>
       <c r="K627" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="L627" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="M627" t="n">
         <v>0</v>
       </c>
       <c r="N627" t="n">
-        <v>9980</v>
+        <v>10121</v>
       </c>
       <c r="O627" t="inlineStr">
         <is>
@@ -48125,32 +48125,32 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
         <is>
-          <t>AI 2415</t>
+          <t>IX 1482</t>
         </is>
       </c>
       <c r="J628" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="K628" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="L628" t="n">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="M628" t="n">
         <v>0</v>
       </c>
       <c r="N628" t="n">
-        <v>10672</v>
+        <v>9980</v>
       </c>
       <c r="O628" t="inlineStr">
         <is>
@@ -48201,12 +48201,12 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
         <is>
-          <t>6E 826</t>
+          <t>AI 2415</t>
         </is>
       </c>
       <c r="J629" t="inlineStr">
@@ -48226,7 +48226,7 @@
         <v>0</v>
       </c>
       <c r="N629" t="n">
-        <v>9795</v>
+        <v>10672</v>
       </c>
       <c r="O629" t="inlineStr">
         <is>
@@ -48282,17 +48282,17 @@
       </c>
       <c r="I630" t="inlineStr">
         <is>
-          <t>6E 842</t>
+          <t>6E 826</t>
         </is>
       </c>
       <c r="J630" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="K630" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="L630" t="n">
@@ -48353,32 +48353,32 @@
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I631" t="inlineStr">
         <is>
-          <t>AI 2485</t>
+          <t>6E 842</t>
         </is>
       </c>
       <c r="J631" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="K631" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="L631" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M631" t="n">
         <v>0</v>
       </c>
       <c r="N631" t="n">
-        <v>11937</v>
+        <v>9795</v>
       </c>
       <c r="O631" t="inlineStr">
         <is>
@@ -48429,32 +48429,32 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
         <is>
-          <t>6E 850</t>
+          <t>AI 2485</t>
         </is>
       </c>
       <c r="J632" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="K632" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="L632" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="M632" t="n">
         <v>0</v>
       </c>
       <c r="N632" t="n">
-        <v>9795</v>
+        <v>11937</v>
       </c>
       <c r="O632" t="inlineStr">
         <is>
@@ -48505,32 +48505,32 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
         <is>
-          <t>AI 2417</t>
+          <t>6E 850</t>
         </is>
       </c>
       <c r="J633" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="K633" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="L633" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M633" t="n">
         <v>0</v>
       </c>
       <c r="N633" t="n">
-        <v>12137</v>
+        <v>9795</v>
       </c>
       <c r="O633" t="inlineStr">
         <is>
@@ -48581,22 +48581,22 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
         <is>
-          <t>6E 176</t>
+          <t>AI 2417</t>
         </is>
       </c>
       <c r="J634" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K634" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="L634" t="n">
@@ -48606,7 +48606,7 @@
         <v>0</v>
       </c>
       <c r="N634" t="n">
-        <v>9795</v>
+        <v>12137</v>
       </c>
       <c r="O634" t="inlineStr">
         <is>
@@ -48662,17 +48662,17 @@
       </c>
       <c r="I635" t="inlineStr">
         <is>
-          <t>6E 828</t>
+          <t>6E 176</t>
         </is>
       </c>
       <c r="J635" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="K635" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="L635" t="n">
@@ -48682,7 +48682,7 @@
         <v>0</v>
       </c>
       <c r="N635" t="n">
-        <v>10096</v>
+        <v>9795</v>
       </c>
       <c r="O635" t="inlineStr">
         <is>
@@ -48733,22 +48733,22 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
         <is>
-          <t>AI 2819</t>
+          <t>6E 828</t>
         </is>
       </c>
       <c r="J636" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="K636" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="L636" t="n">
@@ -48758,7 +48758,7 @@
         <v>0</v>
       </c>
       <c r="N636" t="n">
-        <v>12137</v>
+        <v>10096</v>
       </c>
       <c r="O636" t="inlineStr">
         <is>
@@ -48809,22 +48809,22 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
         <is>
-          <t>6E 880</t>
+          <t>AI 2819</t>
         </is>
       </c>
       <c r="J637" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="K637" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="L637" t="n">
@@ -48834,7 +48834,7 @@
         <v>0</v>
       </c>
       <c r="N637" t="n">
-        <v>9795</v>
+        <v>12137</v>
       </c>
       <c r="O637" t="inlineStr">
         <is>
@@ -48885,22 +48885,22 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
         <is>
-          <t>AI 2797</t>
+          <t>6E 880</t>
         </is>
       </c>
       <c r="J638" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="K638" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="L638" t="n">
@@ -48910,7 +48910,7 @@
         <v>0</v>
       </c>
       <c r="N638" t="n">
-        <v>10032</v>
+        <v>9795</v>
       </c>
       <c r="O638" t="inlineStr">
         <is>
@@ -48961,32 +48961,32 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
         <is>
-          <t>QP 1822</t>
+          <t>AI 2797</t>
         </is>
       </c>
       <c r="J639" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K639" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="L639" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M639" t="n">
         <v>0</v>
       </c>
       <c r="N639" t="n">
-        <v>10147</v>
+        <v>10032</v>
       </c>
       <c r="O639" t="inlineStr">
         <is>
@@ -49037,32 +49037,32 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>6E 837</t>
+          <t>QP 1822</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="K640" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="L640" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M640" t="n">
         <v>0</v>
       </c>
       <c r="N640" t="n">
-        <v>9795</v>
+        <v>10147</v>
       </c>
       <c r="O640" t="inlineStr">
         <is>
@@ -49113,22 +49113,22 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
         <is>
-          <t>AI 2420</t>
+          <t>6E 837</t>
         </is>
       </c>
       <c r="J641" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K641" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="L641" t="n">
@@ -49138,7 +49138,7 @@
         <v>0</v>
       </c>
       <c r="N641" t="n">
-        <v>10032</v>
+        <v>9795</v>
       </c>
       <c r="O641" t="inlineStr">
         <is>
@@ -49189,32 +49189,32 @@
       </c>
       <c r="H642" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I642" t="inlineStr">
         <is>
-          <t>6E 811</t>
+          <t>AI 2420</t>
         </is>
       </c>
       <c r="J642" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="K642" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="L642" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M642" t="n">
         <v>0</v>
       </c>
       <c r="N642" t="n">
-        <v>10096</v>
+        <v>10032</v>
       </c>
       <c r="O642" t="inlineStr">
         <is>
@@ -49265,32 +49265,32 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
         <is>
-          <t>AI 2487</t>
+          <t>6E 811</t>
         </is>
       </c>
       <c r="J643" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="K643" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="L643" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M643" t="n">
         <v>0</v>
       </c>
       <c r="N643" t="n">
-        <v>11381</v>
+        <v>10096</v>
       </c>
       <c r="O643" t="inlineStr">
         <is>
@@ -49341,22 +49341,22 @@
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I644" t="inlineStr">
         <is>
-          <t>IX 1070</t>
+          <t>AI 2487</t>
         </is>
       </c>
       <c r="J644" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="K644" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="L644" t="n">
@@ -49366,7 +49366,7 @@
         <v>0</v>
       </c>
       <c r="N644" t="n">
-        <v>11172</v>
+        <v>11381</v>
       </c>
       <c r="O644" t="inlineStr">
         <is>
@@ -49417,22 +49417,22 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
         <is>
-          <t>AI 2512</t>
+          <t>IX 1070</t>
         </is>
       </c>
       <c r="J645" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K645" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="L645" t="n">
@@ -49442,7 +49442,7 @@
         <v>0</v>
       </c>
       <c r="N645" t="n">
-        <v>11381</v>
+        <v>11172</v>
       </c>
       <c r="O645" t="inlineStr">
         <is>
@@ -49498,27 +49498,27 @@
       </c>
       <c r="I646" t="inlineStr">
         <is>
-          <t>AI 2809</t>
+          <t>AI 2512</t>
         </is>
       </c>
       <c r="J646" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K646" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="L646" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M646" t="n">
         <v>0</v>
       </c>
       <c r="N646" t="n">
-        <v>11187</v>
+        <v>11381</v>
       </c>
       <c r="O646" t="inlineStr">
         <is>
@@ -49569,12 +49569,12 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
         <is>
-          <t>6E 861</t>
+          <t>AI 2809</t>
         </is>
       </c>
       <c r="J647" t="inlineStr">
@@ -49584,17 +49584,17 @@
       </c>
       <c r="K647" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="L647" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M647" t="n">
         <v>0</v>
       </c>
       <c r="N647" t="n">
-        <v>9795</v>
+        <v>11187</v>
       </c>
       <c r="O647" t="inlineStr">
         <is>
@@ -49645,26 +49645,26 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
         <is>
-          <t>QP 1824</t>
+          <t>6E 861</t>
         </is>
       </c>
       <c r="J648" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K648" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="L648" t="n">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="M648" t="n">
         <v>0</v>
@@ -49721,32 +49721,32 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
         <is>
-          <t>6E 6515</t>
+          <t>QP 1824</t>
         </is>
       </c>
       <c r="J649" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K649" t="inlineStr">
         <is>
-          <t>23:40</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="L649" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M649" t="n">
         <v>0</v>
       </c>
       <c r="N649" t="n">
-        <v>10573</v>
+        <v>9795</v>
       </c>
       <c r="O649" t="inlineStr">
         <is>
@@ -49797,22 +49797,22 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
         <is>
-          <t>QP 1308</t>
+          <t>6E 6515</t>
         </is>
       </c>
       <c r="J650" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="K650" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>23:40</t>
         </is>
       </c>
       <c r="L650" t="n">
@@ -49822,7 +49822,7 @@
         <v>0</v>
       </c>
       <c r="N650" t="n">
-        <v>10515</v>
+        <v>10573</v>
       </c>
       <c r="O650" t="inlineStr">
         <is>
@@ -49873,22 +49873,22 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
         <is>
-          <t>AI 2412</t>
+          <t>QP 1308</t>
         </is>
       </c>
       <c r="J651" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="K651" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="L651" t="n">
@@ -49898,7 +49898,7 @@
         <v>0</v>
       </c>
       <c r="N651" t="n">
-        <v>10672</v>
+        <v>10515</v>
       </c>
       <c r="O651" t="inlineStr">
         <is>
@@ -49949,32 +49949,32 @@
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I652" t="inlineStr">
         <is>
-          <t>QP 1350</t>
+          <t>AI 2412</t>
         </is>
       </c>
       <c r="J652" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K652" t="inlineStr">
         <is>
-          <t>00:45</t>
+          <t>00:25</t>
         </is>
       </c>
       <c r="L652" t="n">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M652" t="n">
         <v>0</v>
       </c>
       <c r="N652" t="n">
-        <v>10147</v>
+        <v>10672</v>
       </c>
       <c r="O652" t="inlineStr">
         <is>
@@ -50025,32 +50025,32 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
         <is>
-          <t>6E 846</t>
+          <t>QP 1350</t>
         </is>
       </c>
       <c r="J653" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="K653" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>00:45</t>
         </is>
       </c>
       <c r="L653" t="n">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="M653" t="n">
         <v>0</v>
       </c>
       <c r="N653" t="n">
-        <v>9795</v>
+        <v>10147</v>
       </c>
       <c r="O653" t="inlineStr">
         <is>
@@ -50101,22 +50101,22 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
         <is>
-          <t>AI 2755</t>
+          <t>6E 846</t>
         </is>
       </c>
       <c r="J654" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="K654" t="inlineStr">
         <is>
-          <t>01:25</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="L654" t="n">
@@ -50126,7 +50126,7 @@
         <v>0</v>
       </c>
       <c r="N654" t="n">
-        <v>10032</v>
+        <v>9795</v>
       </c>
       <c r="O654" t="inlineStr">
         <is>
@@ -50177,22 +50177,22 @@
       </c>
       <c r="H655" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I655" t="inlineStr">
         <is>
-          <t>QP 1812</t>
+          <t>AI 2755</t>
         </is>
       </c>
       <c r="J655" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="K655" t="inlineStr">
         <is>
-          <t>01:50</t>
+          <t>01:25</t>
         </is>
       </c>
       <c r="L655" t="n">
@@ -50202,7 +50202,7 @@
         <v>0</v>
       </c>
       <c r="N655" t="n">
-        <v>9795</v>
+        <v>10032</v>
       </c>
       <c r="O655" t="inlineStr">
         <is>
@@ -50253,22 +50253,22 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
         <is>
-          <t>6E 871</t>
+          <t>QP 1812</t>
         </is>
       </c>
       <c r="J656" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="K656" t="inlineStr">
         <is>
-          <t>02:25</t>
+          <t>01:50</t>
         </is>
       </c>
       <c r="L656" t="n">
@@ -50304,7 +50304,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>DEL-BOM</t>
+          <t>DEL-BLR</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -50314,47 +50314,47 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>BOM</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>AI 2615</t>
+          <t>6E 871</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="K657" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>02:25</t>
         </is>
       </c>
       <c r="L657" t="n">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="M657" t="n">
         <v>0</v>
       </c>
       <c r="N657" t="n">
-        <v>8252</v>
+        <v>9795</v>
       </c>
       <c r="O657" t="inlineStr">
         <is>
@@ -50405,32 +50405,32 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
         <is>
-          <t>SG 510</t>
+          <t>AI 2615</t>
         </is>
       </c>
       <c r="J658" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="K658" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="L658" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M658" t="n">
         <v>0</v>
       </c>
       <c r="N658" t="n">
-        <v>6487</v>
+        <v>8252</v>
       </c>
       <c r="O658" t="inlineStr">
         <is>
@@ -50481,32 +50481,32 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>AI 1745</t>
+          <t>SG 510</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="K659" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="L659" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M659" t="n">
         <v>0</v>
       </c>
       <c r="N659" t="n">
-        <v>8252</v>
+        <v>6487</v>
       </c>
       <c r="O659" t="inlineStr">
         <is>
@@ -50557,32 +50557,32 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>IX 1605</t>
+          <t>AI 1745</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="K660" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="L660" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M660" t="n">
         <v>0</v>
       </c>
       <c r="N660" t="n">
-        <v>7148</v>
+        <v>8252</v>
       </c>
       <c r="O660" t="inlineStr">
         <is>
@@ -50633,32 +50633,32 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>6E 6218</t>
+          <t>IX 1605</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="K661" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="L661" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M661" t="n">
         <v>0</v>
       </c>
       <c r="N661" t="n">
-        <v>6963</v>
+        <v>7148</v>
       </c>
       <c r="O661" t="inlineStr">
         <is>
@@ -50709,32 +50709,32 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
         <is>
-          <t>AI 2975</t>
+          <t>6E 6218</t>
         </is>
       </c>
       <c r="J662" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="K662" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="L662" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M662" t="n">
         <v>0</v>
       </c>
       <c r="N662" t="n">
-        <v>7501</v>
+        <v>6963</v>
       </c>
       <c r="O662" t="inlineStr">
         <is>
@@ -50785,22 +50785,22 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
         <is>
-          <t>QP 1833</t>
+          <t>AI 2975</t>
         </is>
       </c>
       <c r="J663" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="K663" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="L663" t="n">
@@ -50810,7 +50810,7 @@
         <v>0</v>
       </c>
       <c r="N663" t="n">
-        <v>6964</v>
+        <v>7501</v>
       </c>
       <c r="O663" t="inlineStr">
         <is>
@@ -50861,32 +50861,32 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>AI 2429</t>
+          <t>QP 1833</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="K664" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="L664" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M664" t="n">
         <v>0</v>
       </c>
       <c r="N664" t="n">
-        <v>8252</v>
+        <v>6964</v>
       </c>
       <c r="O664" t="inlineStr">
         <is>
@@ -50942,17 +50942,17 @@
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>AI 2943</t>
+          <t>AI 2429</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="K665" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="L665" t="n">
@@ -51013,32 +51013,32 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>6E 320</t>
+          <t>AI 2943</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="K666" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="L666" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M666" t="n">
         <v>0</v>
       </c>
       <c r="N666" t="n">
-        <v>6963</v>
+        <v>8252</v>
       </c>
       <c r="O666" t="inlineStr">
         <is>
@@ -51089,32 +51089,32 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>AI 2678</t>
+          <t>6E 320</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="K667" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="L667" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M667" t="n">
         <v>0</v>
       </c>
       <c r="N667" t="n">
-        <v>8252</v>
+        <v>6963</v>
       </c>
       <c r="O667" t="inlineStr">
         <is>
@@ -51165,32 +51165,32 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>QP 1119</t>
+          <t>AI 2678</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="K668" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="L668" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M668" t="n">
         <v>0</v>
       </c>
       <c r="N668" t="n">
-        <v>6964</v>
+        <v>8252</v>
       </c>
       <c r="O668" t="inlineStr">
         <is>
@@ -51241,17 +51241,17 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>6E 675</t>
+          <t>QP 1119</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="K669" t="inlineStr">
@@ -51260,13 +51260,13 @@
         </is>
       </c>
       <c r="L669" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M669" t="n">
         <v>0</v>
       </c>
       <c r="N669" t="n">
-        <v>6963</v>
+        <v>6964</v>
       </c>
       <c r="O669" t="inlineStr">
         <is>
@@ -51317,22 +51317,22 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
         <is>
-          <t>AI 2963</t>
+          <t>6E 675</t>
         </is>
       </c>
       <c r="J670" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="K670" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="L670" t="n">
@@ -51342,7 +51342,7 @@
         <v>0</v>
       </c>
       <c r="N670" t="n">
-        <v>8252</v>
+        <v>6963</v>
       </c>
       <c r="O670" t="inlineStr">
         <is>
@@ -51393,32 +51393,32 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
         <is>
-          <t>SG 815</t>
+          <t>AI 2963</t>
         </is>
       </c>
       <c r="J671" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="K671" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="L671" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M671" t="n">
         <v>0</v>
       </c>
       <c r="N671" t="n">
-        <v>7719</v>
+        <v>8252</v>
       </c>
       <c r="O671" t="inlineStr">
         <is>
@@ -51469,32 +51469,32 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
         <is>
-          <t>QP 1112</t>
+          <t>SG 815</t>
         </is>
       </c>
       <c r="J672" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="K672" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="L672" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M672" t="n">
         <v>0</v>
       </c>
       <c r="N672" t="n">
-        <v>6964</v>
+        <v>7719</v>
       </c>
       <c r="O672" t="inlineStr">
         <is>
@@ -51545,32 +51545,32 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>AI 2927</t>
+          <t>QP 1112</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="K673" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="L673" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="M673" t="n">
         <v>0</v>
       </c>
       <c r="N673" t="n">
-        <v>8252</v>
+        <v>6964</v>
       </c>
       <c r="O673" t="inlineStr">
         <is>
@@ -51621,12 +51621,12 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>6E 6107</t>
+          <t>AI 2927</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -51636,17 +51636,17 @@
       </c>
       <c r="K674" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="L674" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M674" t="n">
         <v>0</v>
       </c>
       <c r="N674" t="n">
-        <v>6963</v>
+        <v>8252</v>
       </c>
       <c r="O674" t="inlineStr">
         <is>
@@ -51697,32 +51697,32 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>QP 1110</t>
+          <t>6E 6107</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="K675" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="L675" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M675" t="n">
         <v>0</v>
       </c>
       <c r="N675" t="n">
-        <v>6964</v>
+        <v>6963</v>
       </c>
       <c r="O675" t="inlineStr">
         <is>
@@ -51773,32 +51773,32 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>6E 6328</t>
+          <t>QP 1110</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="K676" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="L676" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M676" t="n">
         <v>0</v>
       </c>
       <c r="N676" t="n">
-        <v>6963</v>
+        <v>6964</v>
       </c>
       <c r="O676" t="inlineStr">
         <is>
@@ -51849,22 +51849,22 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>AI 2425</t>
+          <t>6E 6328</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="K677" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="L677" t="n">
@@ -51874,7 +51874,7 @@
         <v>0</v>
       </c>
       <c r="N677" t="n">
-        <v>8252</v>
+        <v>6963</v>
       </c>
       <c r="O677" t="inlineStr">
         <is>
@@ -51930,27 +51930,27 @@
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>AI 2945</t>
+          <t>AI 2425</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="K678" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="L678" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M678" t="n">
         <v>0</v>
       </c>
       <c r="N678" t="n">
-        <v>8603</v>
+        <v>8252</v>
       </c>
       <c r="O678" t="inlineStr">
         <is>
@@ -52001,12 +52001,12 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
         <is>
-          <t>6E 6047</t>
+          <t>AI 2945</t>
         </is>
       </c>
       <c r="J679" t="inlineStr">
@@ -52016,17 +52016,17 @@
       </c>
       <c r="K679" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="L679" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M679" t="n">
         <v>0</v>
       </c>
       <c r="N679" t="n">
-        <v>6963</v>
+        <v>8603</v>
       </c>
       <c r="O679" t="inlineStr">
         <is>
@@ -52077,32 +52077,32 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>AI 1785</t>
+          <t>6E 6047</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K680" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="L680" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M680" t="n">
         <v>0</v>
       </c>
       <c r="N680" t="n">
-        <v>8252</v>
+        <v>6963</v>
       </c>
       <c r="O680" t="inlineStr">
         <is>
@@ -52153,12 +52153,12 @@
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>6E 6676</t>
+          <t>AI 1785</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -52168,17 +52168,17 @@
       </c>
       <c r="K681" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="L681" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M681" t="n">
         <v>0</v>
       </c>
       <c r="N681" t="n">
-        <v>7593</v>
+        <v>8252</v>
       </c>
       <c r="O681" t="inlineStr">
         <is>
@@ -52229,32 +52229,32 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>QP 1836</t>
+          <t>6E 6676</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="K682" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="L682" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M682" t="n">
         <v>0</v>
       </c>
       <c r="N682" t="n">
-        <v>7186</v>
+        <v>7593</v>
       </c>
       <c r="O682" t="inlineStr">
         <is>
@@ -52305,32 +52305,32 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>6E 324</t>
+          <t>QP 1836</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="K683" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="L683" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M683" t="n">
         <v>0</v>
       </c>
       <c r="N683" t="n">
-        <v>7225</v>
+        <v>7186</v>
       </c>
       <c r="O683" t="inlineStr">
         <is>
@@ -52381,32 +52381,32 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>AI 2951</t>
+          <t>6E 324</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K684" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="L684" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M684" t="n">
         <v>0</v>
       </c>
       <c r="N684" t="n">
-        <v>8603</v>
+        <v>7225</v>
       </c>
       <c r="O684" t="inlineStr">
         <is>
@@ -52457,32 +52457,32 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
         <is>
-          <t>6E 6022</t>
+          <t>AI 2951</t>
         </is>
       </c>
       <c r="J685" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K685" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="L685" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M685" t="n">
         <v>0</v>
       </c>
       <c r="N685" t="n">
-        <v>7593</v>
+        <v>8603</v>
       </c>
       <c r="O685" t="inlineStr">
         <is>
@@ -52538,21 +52538,21 @@
       </c>
       <c r="I686" t="inlineStr">
         <is>
-          <t>6E 6318</t>
+          <t>6E 6022</t>
         </is>
       </c>
       <c r="J686" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K686" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="L686" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M686" t="n">
         <v>0</v>
@@ -52609,12 +52609,12 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>SG 808</t>
+          <t>6E 6318</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -52624,17 +52624,17 @@
       </c>
       <c r="K687" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="L687" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M687" t="n">
         <v>0</v>
       </c>
       <c r="N687" t="n">
-        <v>7719</v>
+        <v>7593</v>
       </c>
       <c r="O687" t="inlineStr">
         <is>
@@ -52685,32 +52685,32 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>AI 2933</t>
+          <t>SG 808</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="K688" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="L688" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M688" t="n">
         <v>0</v>
       </c>
       <c r="N688" t="n">
-        <v>8603</v>
+        <v>7719</v>
       </c>
       <c r="O688" t="inlineStr">
         <is>
@@ -52761,12 +52761,12 @@
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
         <is>
-          <t>6E 864</t>
+          <t>AI 2933</t>
         </is>
       </c>
       <c r="J689" t="inlineStr">
@@ -52776,17 +52776,17 @@
       </c>
       <c r="K689" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="L689" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M689" t="n">
         <v>0</v>
       </c>
       <c r="N689" t="n">
-        <v>7225</v>
+        <v>8603</v>
       </c>
       <c r="O689" t="inlineStr">
         <is>
@@ -52837,32 +52837,32 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>AI 1777</t>
+          <t>6E 864</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="K690" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="L690" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M690" t="n">
         <v>0</v>
       </c>
       <c r="N690" t="n">
-        <v>8462</v>
+        <v>7225</v>
       </c>
       <c r="O690" t="inlineStr">
         <is>
@@ -52913,12 +52913,12 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
         <is>
-          <t>QP 1128</t>
+          <t>AI 1777</t>
         </is>
       </c>
       <c r="J691" t="inlineStr">
@@ -52928,17 +52928,17 @@
       </c>
       <c r="K691" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="L691" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M691" t="n">
         <v>0</v>
       </c>
       <c r="N691" t="n">
-        <v>7658</v>
+        <v>8462</v>
       </c>
       <c r="O691" t="inlineStr">
         <is>
@@ -52989,22 +52989,22 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>6E 327</t>
+          <t>QP 1128</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K692" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="L692" t="n">
@@ -53014,7 +53014,7 @@
         <v>0</v>
       </c>
       <c r="N692" t="n">
-        <v>7225</v>
+        <v>7658</v>
       </c>
       <c r="O692" t="inlineStr">
         <is>
@@ -53065,22 +53065,22 @@
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>AI 2941</t>
+          <t>6E 327</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K693" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="L693" t="n">
@@ -53090,7 +53090,7 @@
         <v>0</v>
       </c>
       <c r="N693" t="n">
-        <v>8603</v>
+        <v>7225</v>
       </c>
       <c r="O693" t="inlineStr">
         <is>
@@ -53141,32 +53141,32 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>6E 6706</t>
+          <t>AI 2941</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K694" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="L694" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M694" t="n">
         <v>0</v>
       </c>
       <c r="N694" t="n">
-        <v>7593</v>
+        <v>8603</v>
       </c>
       <c r="O694" t="inlineStr">
         <is>
@@ -53217,32 +53217,32 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>AI 2751</t>
+          <t>6E 6706</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K695" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="L695" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M695" t="n">
         <v>0</v>
       </c>
       <c r="N695" t="n">
-        <v>8252</v>
+        <v>7593</v>
       </c>
       <c r="O695" t="inlineStr">
         <is>
@@ -53293,12 +53293,12 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>QP 1820</t>
+          <t>AI 2751</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
@@ -53308,17 +53308,17 @@
       </c>
       <c r="K696" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="L696" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M696" t="n">
         <v>0</v>
       </c>
       <c r="N696" t="n">
-        <v>7658</v>
+        <v>8252</v>
       </c>
       <c r="O696" t="inlineStr">
         <is>
@@ -53369,32 +53369,32 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>IX 1056</t>
+          <t>QP 1820</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="K697" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="L697" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M697" t="n">
         <v>0</v>
       </c>
       <c r="N697" t="n">
-        <v>8208</v>
+        <v>7658</v>
       </c>
       <c r="O697" t="inlineStr">
         <is>
@@ -53445,32 +53445,32 @@
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
         <is>
-          <t>AI 2955</t>
+          <t>IX 1056</t>
         </is>
       </c>
       <c r="J698" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="K698" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="L698" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M698" t="n">
         <v>0</v>
       </c>
       <c r="N698" t="n">
-        <v>8462</v>
+        <v>8208</v>
       </c>
       <c r="O698" t="inlineStr">
         <is>
@@ -53521,12 +53521,12 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
         <is>
-          <t>6E 329</t>
+          <t>AI 2955</t>
         </is>
       </c>
       <c r="J699" t="inlineStr">
@@ -53536,17 +53536,17 @@
       </c>
       <c r="K699" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="L699" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M699" t="n">
         <v>0</v>
       </c>
       <c r="N699" t="n">
-        <v>7960</v>
+        <v>8462</v>
       </c>
       <c r="O699" t="inlineStr">
         <is>
@@ -53597,32 +53597,32 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>AI 2441</t>
+          <t>6E 329</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="K700" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="L700" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="M700" t="n">
         <v>0</v>
       </c>
       <c r="N700" t="n">
-        <v>8325</v>
+        <v>7960</v>
       </c>
       <c r="O700" t="inlineStr">
         <is>
@@ -53673,32 +53673,32 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
         <is>
-          <t>SG 476</t>
+          <t>AI 2441</t>
         </is>
       </c>
       <c r="J701" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="K701" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="L701" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="M701" t="n">
         <v>0</v>
       </c>
       <c r="N701" t="n">
-        <v>7335</v>
+        <v>8325</v>
       </c>
       <c r="O701" t="inlineStr">
         <is>
@@ -53749,32 +53749,32 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
         <is>
-          <t>AI 2977</t>
+          <t>SG 476</t>
         </is>
       </c>
       <c r="J702" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K702" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="L702" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="M702" t="n">
         <v>0</v>
       </c>
       <c r="N702" t="n">
-        <v>8462</v>
+        <v>7335</v>
       </c>
       <c r="O702" t="inlineStr">
         <is>
@@ -53825,12 +53825,12 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
         <is>
-          <t>6E 354</t>
+          <t>AI 2977</t>
         </is>
       </c>
       <c r="J703" t="inlineStr">
@@ -53850,7 +53850,7 @@
         <v>0</v>
       </c>
       <c r="N703" t="n">
-        <v>7593</v>
+        <v>8462</v>
       </c>
       <c r="O703" t="inlineStr">
         <is>
@@ -53901,22 +53901,22 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
         <is>
-          <t>AI 2985</t>
+          <t>6E 354</t>
         </is>
       </c>
       <c r="J704" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K704" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="L704" t="n">
@@ -53926,7 +53926,7 @@
         <v>0</v>
       </c>
       <c r="N704" t="n">
-        <v>8462</v>
+        <v>7593</v>
       </c>
       <c r="O704" t="inlineStr">
         <is>
@@ -53977,22 +53977,22 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
         <is>
-          <t>QP 1826</t>
+          <t>AI 2985</t>
         </is>
       </c>
       <c r="J705" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K705" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="L705" t="n">
@@ -54002,7 +54002,7 @@
         <v>0</v>
       </c>
       <c r="N705" t="n">
-        <v>7658</v>
+        <v>8462</v>
       </c>
       <c r="O705" t="inlineStr">
         <is>
@@ -54053,22 +54053,22 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
         <is>
-          <t>AI 2805</t>
+          <t>QP 1826</t>
         </is>
       </c>
       <c r="J706" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="K706" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="L706" t="n">
@@ -54078,7 +54078,7 @@
         <v>0</v>
       </c>
       <c r="N706" t="n">
-        <v>8603</v>
+        <v>7658</v>
       </c>
       <c r="O706" t="inlineStr">
         <is>
@@ -54129,12 +54129,12 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
         <is>
-          <t>6E 303</t>
+          <t>AI 2805</t>
         </is>
       </c>
       <c r="J707" t="inlineStr">
@@ -54144,17 +54144,17 @@
       </c>
       <c r="K707" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="L707" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M707" t="n">
         <v>0</v>
       </c>
       <c r="N707" t="n">
-        <v>7225</v>
+        <v>8603</v>
       </c>
       <c r="O707" t="inlineStr">
         <is>
@@ -54205,32 +54205,32 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
         <is>
-          <t>SG 162</t>
+          <t>6E 303</t>
         </is>
       </c>
       <c r="J708" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K708" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="L708" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M708" t="n">
         <v>0</v>
       </c>
       <c r="N708" t="n">
-        <v>6988</v>
+        <v>7225</v>
       </c>
       <c r="O708" t="inlineStr">
         <is>
@@ -54281,32 +54281,32 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
         <is>
-          <t>AI 2957</t>
+          <t>SG 162</t>
         </is>
       </c>
       <c r="J709" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K709" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="L709" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="M709" t="n">
         <v>0</v>
       </c>
       <c r="N709" t="n">
-        <v>8603</v>
+        <v>6988</v>
       </c>
       <c r="O709" t="inlineStr">
         <is>
@@ -54357,17 +54357,17 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
         <is>
-          <t>6E 853</t>
+          <t>AI 2957</t>
         </is>
       </c>
       <c r="J710" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K710" t="inlineStr">
@@ -54376,13 +54376,13 @@
         </is>
       </c>
       <c r="L710" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="M710" t="n">
         <v>0</v>
       </c>
       <c r="N710" t="n">
-        <v>7225</v>
+        <v>8603</v>
       </c>
       <c r="O710" t="inlineStr">
         <is>
@@ -54433,32 +54433,32 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
         <is>
-          <t>AI 2981</t>
+          <t>6E 853</t>
         </is>
       </c>
       <c r="J711" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="K711" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="L711" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M711" t="n">
         <v>0</v>
       </c>
       <c r="N711" t="n">
-        <v>8672</v>
+        <v>7225</v>
       </c>
       <c r="O711" t="inlineStr">
         <is>
@@ -54509,12 +54509,12 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>SG 800</t>
+          <t>AI 2981</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
@@ -54524,17 +54524,17 @@
       </c>
       <c r="K712" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="L712" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="M712" t="n">
         <v>0</v>
       </c>
       <c r="N712" t="n">
-        <v>6988</v>
+        <v>8672</v>
       </c>
       <c r="O712" t="inlineStr">
         <is>
@@ -54585,32 +54585,32 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
         <is>
-          <t>AI 2433</t>
+          <t>SG 800</t>
         </is>
       </c>
       <c r="J713" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K713" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="L713" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="M713" t="n">
         <v>0</v>
       </c>
       <c r="N713" t="n">
-        <v>8462</v>
+        <v>6988</v>
       </c>
       <c r="O713" t="inlineStr">
         <is>
@@ -54661,32 +54661,32 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
         <is>
-          <t>6E 395</t>
+          <t>AI 2433</t>
         </is>
       </c>
       <c r="J714" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K714" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="L714" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M714" t="n">
         <v>0</v>
       </c>
       <c r="N714" t="n">
-        <v>7225</v>
+        <v>8462</v>
       </c>
       <c r="O714" t="inlineStr">
         <is>
@@ -54737,32 +54737,32 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
         <is>
-          <t>AI 2999</t>
+          <t>6E 395</t>
         </is>
       </c>
       <c r="J715" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="K715" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="L715" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M715" t="n">
         <v>0</v>
       </c>
       <c r="N715" t="n">
-        <v>8252</v>
+        <v>7225</v>
       </c>
       <c r="O715" t="inlineStr">
         <is>
@@ -54818,17 +54818,17 @@
       </c>
       <c r="I716" t="inlineStr">
         <is>
-          <t>AI 2437</t>
+          <t>AI 2999</t>
         </is>
       </c>
       <c r="J716" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="K716" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>00:25</t>
         </is>
       </c>
       <c r="L716" t="n">
@@ -54889,12 +54889,12 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
         <is>
-          <t>SG 802</t>
+          <t>AI 2437</t>
         </is>
       </c>
       <c r="J717" t="inlineStr">
@@ -54904,17 +54904,17 @@
       </c>
       <c r="K717" t="inlineStr">
         <is>
-          <t>00:50</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="L717" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M717" t="n">
         <v>0</v>
       </c>
       <c r="N717" t="n">
-        <v>6697</v>
+        <v>8252</v>
       </c>
       <c r="O717" t="inlineStr">
         <is>
@@ -54965,22 +54965,22 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
         <is>
-          <t>6E 6114</t>
+          <t>SG 802</t>
         </is>
       </c>
       <c r="J718" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="K718" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>00:50</t>
         </is>
       </c>
       <c r="L718" t="n">
@@ -54990,7 +54990,7 @@
         <v>0</v>
       </c>
       <c r="N718" t="n">
-        <v>6963</v>
+        <v>6697</v>
       </c>
       <c r="O718" t="inlineStr">
         <is>
@@ -55041,32 +55041,32 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
         <is>
-          <t>AI 2439</t>
+          <t>6E 6114</t>
         </is>
       </c>
       <c r="J719" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="K719" t="inlineStr">
         <is>
-          <t>01:25</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="L719" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M719" t="n">
         <v>0</v>
       </c>
       <c r="N719" t="n">
-        <v>8252</v>
+        <v>6963</v>
       </c>
       <c r="O719" t="inlineStr">
         <is>
@@ -55117,32 +55117,32 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
         <is>
-          <t>6E 322</t>
+          <t>AI 2439</t>
         </is>
       </c>
       <c r="J720" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="K720" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:25</t>
         </is>
       </c>
       <c r="L720" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M720" t="n">
         <v>0</v>
       </c>
       <c r="N720" t="n">
-        <v>6963</v>
+        <v>8252</v>
       </c>
       <c r="O720" t="inlineStr">
         <is>
@@ -55183,42 +55183,42 @@
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
         <is>
-          <t>AI 2615</t>
+          <t>6E 322</t>
         </is>
       </c>
       <c r="J721" t="inlineStr">
         <is>
-          <t>02:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="K721" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="L721" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M721" t="n">
         <v>0</v>
       </c>
       <c r="N721" t="n">
-        <v>7653</v>
+        <v>6963</v>
       </c>
       <c r="O721" t="inlineStr">
         <is>
@@ -55269,32 +55269,32 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
         <is>
-          <t>SG 510</t>
+          <t>AI 2615</t>
         </is>
       </c>
       <c r="J722" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>02:45</t>
         </is>
       </c>
       <c r="K722" t="inlineStr">
         <is>
-          <t>06:15</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="L722" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M722" t="n">
         <v>0</v>
       </c>
       <c r="N722" t="n">
-        <v>6277</v>
+        <v>7653</v>
       </c>
       <c r="O722" t="inlineStr">
         <is>
@@ -55345,32 +55345,32 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
         <is>
-          <t>AI 1745</t>
+          <t>SG 510</t>
         </is>
       </c>
       <c r="J723" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="K723" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>06:15</t>
         </is>
       </c>
       <c r="L723" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M723" t="n">
         <v>0</v>
       </c>
       <c r="N723" t="n">
-        <v>7653</v>
+        <v>6277</v>
       </c>
       <c r="O723" t="inlineStr">
         <is>
@@ -55421,32 +55421,32 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
         <is>
-          <t>IX 1605</t>
+          <t>AI 1745</t>
         </is>
       </c>
       <c r="J724" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="K724" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="L724" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M724" t="n">
         <v>0</v>
       </c>
       <c r="N724" t="n">
-        <v>7148</v>
+        <v>7653</v>
       </c>
       <c r="O724" t="inlineStr">
         <is>
@@ -55497,32 +55497,32 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
         <is>
-          <t>6E 6218</t>
+          <t>IX 1605</t>
         </is>
       </c>
       <c r="J725" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="K725" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="L725" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="M725" t="n">
         <v>0</v>
       </c>
       <c r="N725" t="n">
-        <v>6963</v>
+        <v>7148</v>
       </c>
       <c r="O725" t="inlineStr">
         <is>
@@ -55573,32 +55573,32 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
         <is>
-          <t>AI 2975</t>
+          <t>6E 6218</t>
         </is>
       </c>
       <c r="J726" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="K726" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="L726" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M726" t="n">
         <v>0</v>
       </c>
       <c r="N726" t="n">
-        <v>7653</v>
+        <v>6963</v>
       </c>
       <c r="O726" t="inlineStr">
         <is>
@@ -55649,22 +55649,22 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
         <is>
-          <t>QP 1833</t>
+          <t>AI 2975</t>
         </is>
       </c>
       <c r="J727" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="L727" t="n">
@@ -55674,7 +55674,7 @@
         <v>0</v>
       </c>
       <c r="N727" t="n">
-        <v>7186</v>
+        <v>7653</v>
       </c>
       <c r="O727" t="inlineStr">
         <is>
@@ -55725,32 +55725,32 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
         <is>
-          <t>AI 2429</t>
+          <t>QP 1833</t>
         </is>
       </c>
       <c r="J728" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="L728" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M728" t="n">
         <v>0</v>
       </c>
       <c r="N728" t="n">
-        <v>7653</v>
+        <v>7186</v>
       </c>
       <c r="O728" t="inlineStr">
         <is>
@@ -55806,17 +55806,17 @@
       </c>
       <c r="I729" t="inlineStr">
         <is>
-          <t>AI 2943</t>
+          <t>AI 2429</t>
         </is>
       </c>
       <c r="J729" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="K729" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="L729" t="n">
@@ -55877,32 +55877,32 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
         <is>
-          <t>6E 320</t>
+          <t>AI 2943</t>
         </is>
       </c>
       <c r="J730" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="K730" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="L730" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M730" t="n">
         <v>0</v>
       </c>
       <c r="N730" t="n">
-        <v>6963</v>
+        <v>7653</v>
       </c>
       <c r="O730" t="inlineStr">
         <is>
@@ -55953,32 +55953,32 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
         <is>
-          <t>AI 2678</t>
+          <t>6E 320</t>
         </is>
       </c>
       <c r="J731" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="K731" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="L731" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M731" t="n">
         <v>0</v>
       </c>
       <c r="N731" t="n">
-        <v>7653</v>
+        <v>6963</v>
       </c>
       <c r="O731" t="inlineStr">
         <is>
@@ -56029,32 +56029,32 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
         <is>
-          <t>QP 1119</t>
+          <t>AI 2678</t>
         </is>
       </c>
       <c r="J732" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="K732" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="L732" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M732" t="n">
         <v>0</v>
       </c>
       <c r="N732" t="n">
-        <v>7186</v>
+        <v>7653</v>
       </c>
       <c r="O732" t="inlineStr">
         <is>
@@ -56105,17 +56105,17 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
         <is>
-          <t>6E 675</t>
+          <t>QP 1119</t>
         </is>
       </c>
       <c r="J733" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="K733" t="inlineStr">
@@ -56124,13 +56124,13 @@
         </is>
       </c>
       <c r="L733" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M733" t="n">
         <v>0</v>
       </c>
       <c r="N733" t="n">
-        <v>6963</v>
+        <v>7186</v>
       </c>
       <c r="O733" t="inlineStr">
         <is>
@@ -56181,22 +56181,22 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
         <is>
-          <t>AI 2963</t>
+          <t>6E 675</t>
         </is>
       </c>
       <c r="J734" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="K734" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="L734" t="n">
@@ -56206,7 +56206,7 @@
         <v>0</v>
       </c>
       <c r="N734" t="n">
-        <v>7501</v>
+        <v>6963</v>
       </c>
       <c r="O734" t="inlineStr">
         <is>
@@ -56257,32 +56257,32 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
         <is>
-          <t>SG 815</t>
+          <t>AI 2963</t>
         </is>
       </c>
       <c r="J735" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="K735" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="L735" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M735" t="n">
         <v>0</v>
       </c>
       <c r="N735" t="n">
-        <v>6775</v>
+        <v>7501</v>
       </c>
       <c r="O735" t="inlineStr">
         <is>
@@ -56333,32 +56333,32 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
         <is>
-          <t>QP 1112</t>
+          <t>SG 815</t>
         </is>
       </c>
       <c r="J736" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="K736" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="L736" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M736" t="n">
         <v>0</v>
       </c>
       <c r="N736" t="n">
-        <v>6964</v>
+        <v>6775</v>
       </c>
       <c r="O736" t="inlineStr">
         <is>
@@ -56409,32 +56409,32 @@
       </c>
       <c r="H737" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I737" t="inlineStr">
         <is>
-          <t>AI 2927</t>
+          <t>QP 1112</t>
         </is>
       </c>
       <c r="J737" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="K737" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="L737" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="M737" t="n">
         <v>0</v>
       </c>
       <c r="N737" t="n">
-        <v>7501</v>
+        <v>6964</v>
       </c>
       <c r="O737" t="inlineStr">
         <is>
@@ -56485,12 +56485,12 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
         <is>
-          <t>6E 6107</t>
+          <t>AI 2927</t>
         </is>
       </c>
       <c r="J738" t="inlineStr">
@@ -56500,17 +56500,17 @@
       </c>
       <c r="K738" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="L738" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M738" t="n">
         <v>0</v>
       </c>
       <c r="N738" t="n">
-        <v>6963</v>
+        <v>7501</v>
       </c>
       <c r="O738" t="inlineStr">
         <is>
@@ -56561,32 +56561,32 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
         <is>
-          <t>QP 1110</t>
+          <t>6E 6107</t>
         </is>
       </c>
       <c r="J739" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="K739" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="L739" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M739" t="n">
         <v>0</v>
       </c>
       <c r="N739" t="n">
-        <v>6964</v>
+        <v>6963</v>
       </c>
       <c r="O739" t="inlineStr">
         <is>
@@ -56637,32 +56637,32 @@
       </c>
       <c r="H740" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I740" t="inlineStr">
         <is>
-          <t>6E 6328</t>
+          <t>QP 1110</t>
         </is>
       </c>
       <c r="J740" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="K740" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="L740" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M740" t="n">
         <v>0</v>
       </c>
       <c r="N740" t="n">
-        <v>6963</v>
+        <v>6964</v>
       </c>
       <c r="O740" t="inlineStr">
         <is>
@@ -56713,22 +56713,22 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
         <is>
-          <t>AI 2425</t>
+          <t>6E 6328</t>
         </is>
       </c>
       <c r="J741" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="K741" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="L741" t="n">
@@ -56738,7 +56738,7 @@
         <v>0</v>
       </c>
       <c r="N741" t="n">
-        <v>7501</v>
+        <v>6963</v>
       </c>
       <c r="O741" t="inlineStr">
         <is>
@@ -56794,21 +56794,21 @@
       </c>
       <c r="I742" t="inlineStr">
         <is>
-          <t>AI 2945</t>
+          <t>AI 2425</t>
         </is>
       </c>
       <c r="J742" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="K742" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="L742" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M742" t="n">
         <v>0</v>
@@ -56865,12 +56865,12 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
         <is>
-          <t>6E 6047</t>
+          <t>AI 2945</t>
         </is>
       </c>
       <c r="J743" t="inlineStr">
@@ -56880,17 +56880,17 @@
       </c>
       <c r="K743" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="L743" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M743" t="n">
         <v>0</v>
       </c>
       <c r="N743" t="n">
-        <v>6963</v>
+        <v>7501</v>
       </c>
       <c r="O743" t="inlineStr">
         <is>
@@ -56941,32 +56941,32 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>AI 1785</t>
+          <t>6E 6047</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="K744" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="L744" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M744" t="n">
         <v>0</v>
       </c>
       <c r="N744" t="n">
-        <v>7853</v>
+        <v>6963</v>
       </c>
       <c r="O744" t="inlineStr">
         <is>
@@ -57017,12 +57017,12 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
         <is>
-          <t>6E 6676</t>
+          <t>AI 1785</t>
         </is>
       </c>
       <c r="J745" t="inlineStr">
@@ -57032,17 +57032,17 @@
       </c>
       <c r="K745" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="L745" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M745" t="n">
         <v>0</v>
       </c>
       <c r="N745" t="n">
-        <v>7225</v>
+        <v>7853</v>
       </c>
       <c r="O745" t="inlineStr">
         <is>
@@ -57093,32 +57093,32 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
         <is>
-          <t>QP 1836</t>
+          <t>6E 6676</t>
         </is>
       </c>
       <c r="J746" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="K746" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="L746" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M746" t="n">
         <v>0</v>
       </c>
       <c r="N746" t="n">
-        <v>7186</v>
+        <v>7225</v>
       </c>
       <c r="O746" t="inlineStr">
         <is>
@@ -57169,32 +57169,32 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
         <is>
-          <t>6E 324</t>
+          <t>QP 1836</t>
         </is>
       </c>
       <c r="J747" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="K747" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="L747" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M747" t="n">
         <v>0</v>
       </c>
       <c r="N747" t="n">
-        <v>7225</v>
+        <v>7186</v>
       </c>
       <c r="O747" t="inlineStr">
         <is>
@@ -57245,32 +57245,32 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
         <is>
-          <t>AI 2951</t>
+          <t>6E 324</t>
         </is>
       </c>
       <c r="J748" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K748" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="L748" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M748" t="n">
         <v>0</v>
       </c>
       <c r="N748" t="n">
-        <v>8183</v>
+        <v>7225</v>
       </c>
       <c r="O748" t="inlineStr">
         <is>
@@ -57321,32 +57321,32 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
         <is>
-          <t>6E 6022</t>
+          <t>AI 2951</t>
         </is>
       </c>
       <c r="J749" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="K749" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="L749" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M749" t="n">
         <v>0</v>
       </c>
       <c r="N749" t="n">
-        <v>6963</v>
+        <v>8183</v>
       </c>
       <c r="O749" t="inlineStr">
         <is>
@@ -57402,21 +57402,21 @@
       </c>
       <c r="I750" t="inlineStr">
         <is>
-          <t>6E 6318</t>
+          <t>6E 6022</t>
         </is>
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="K750" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="L750" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M750" t="n">
         <v>0</v>
@@ -57473,12 +57473,12 @@
       </c>
       <c r="H751" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I751" t="inlineStr">
         <is>
-          <t>SG 808</t>
+          <t>6E 6318</t>
         </is>
       </c>
       <c r="J751" t="inlineStr">
@@ -57488,17 +57488,17 @@
       </c>
       <c r="K751" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="L751" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M751" t="n">
         <v>0</v>
       </c>
       <c r="N751" t="n">
-        <v>6775</v>
+        <v>6963</v>
       </c>
       <c r="O751" t="inlineStr">
         <is>
@@ -57549,32 +57549,32 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
         <is>
-          <t>AI 2933</t>
+          <t>SG 808</t>
         </is>
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="K752" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="L752" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M752" t="n">
         <v>0</v>
       </c>
       <c r="N752" t="n">
-        <v>7501</v>
+        <v>6775</v>
       </c>
       <c r="O752" t="inlineStr">
         <is>
@@ -57625,12 +57625,12 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
         <is>
-          <t>6E 864</t>
+          <t>AI 2933</t>
         </is>
       </c>
       <c r="J753" t="inlineStr">
@@ -57640,17 +57640,17 @@
       </c>
       <c r="K753" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="L753" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M753" t="n">
         <v>0</v>
       </c>
       <c r="N753" t="n">
-        <v>6963</v>
+        <v>7501</v>
       </c>
       <c r="O753" t="inlineStr">
         <is>
@@ -57701,32 +57701,32 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
         <is>
-          <t>AI 1777</t>
+          <t>6E 864</t>
         </is>
       </c>
       <c r="J754" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="K754" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="L754" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M754" t="n">
         <v>0</v>
       </c>
       <c r="N754" t="n">
-        <v>7501</v>
+        <v>6963</v>
       </c>
       <c r="O754" t="inlineStr">
         <is>
@@ -57777,12 +57777,12 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
         <is>
-          <t>QP 1128</t>
+          <t>AI 1777</t>
         </is>
       </c>
       <c r="J755" t="inlineStr">
@@ -57792,17 +57792,17 @@
       </c>
       <c r="K755" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="L755" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M755" t="n">
         <v>0</v>
       </c>
       <c r="N755" t="n">
-        <v>6964</v>
+        <v>7501</v>
       </c>
       <c r="O755" t="inlineStr">
         <is>
@@ -57853,22 +57853,22 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
         <is>
-          <t>6E 327</t>
+          <t>QP 1128</t>
         </is>
       </c>
       <c r="J756" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="K756" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="L756" t="n">
@@ -57878,7 +57878,7 @@
         <v>0</v>
       </c>
       <c r="N756" t="n">
-        <v>6963</v>
+        <v>6964</v>
       </c>
       <c r="O756" t="inlineStr">
         <is>
@@ -57929,22 +57929,22 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
         <is>
-          <t>AI 2941</t>
+          <t>6E 327</t>
         </is>
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="K757" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="L757" t="n">
@@ -57954,7 +57954,7 @@
         <v>0</v>
       </c>
       <c r="N757" t="n">
-        <v>8603</v>
+        <v>6963</v>
       </c>
       <c r="O757" t="inlineStr">
         <is>
@@ -58005,32 +58005,32 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
         <is>
-          <t>6E 6706</t>
+          <t>AI 2941</t>
         </is>
       </c>
       <c r="J758" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="K758" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="L758" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="M758" t="n">
         <v>0</v>
       </c>
       <c r="N758" t="n">
-        <v>7593</v>
+        <v>8603</v>
       </c>
       <c r="O758" t="inlineStr">
         <is>
@@ -58081,32 +58081,32 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
         <is>
-          <t>AI 2751</t>
+          <t>6E 6706</t>
         </is>
       </c>
       <c r="J759" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="K759" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="L759" t="n">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="M759" t="n">
         <v>0</v>
       </c>
       <c r="N759" t="n">
-        <v>7853</v>
+        <v>7593</v>
       </c>
       <c r="O759" t="inlineStr">
         <is>
@@ -58157,12 +58157,12 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
         <is>
-          <t>QP 1820</t>
+          <t>AI 2751</t>
         </is>
       </c>
       <c r="J760" t="inlineStr">
@@ -58172,17 +58172,17 @@
       </c>
       <c r="K760" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="L760" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M760" t="n">
         <v>0</v>
       </c>
       <c r="N760" t="n">
-        <v>7418</v>
+        <v>7853</v>
       </c>
       <c r="O760" t="inlineStr">
         <is>
@@ -58233,32 +58233,32 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
         <is>
-          <t>IX 1056</t>
+          <t>QP 1820</t>
         </is>
       </c>
       <c r="J761" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="K761" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="L761" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M761" t="n">
         <v>0</v>
       </c>
       <c r="N761" t="n">
-        <v>7148</v>
+        <v>7418</v>
       </c>
       <c r="O761" t="inlineStr">
         <is>
@@ -58309,32 +58309,32 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
         <is>
-          <t>AI 2955</t>
+          <t>IX 1056</t>
         </is>
       </c>
       <c r="J762" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="K762" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="L762" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M762" t="n">
         <v>0</v>
       </c>
       <c r="N762" t="n">
-        <v>8052</v>
+        <v>7148</v>
       </c>
       <c r="O762" t="inlineStr">
         <is>
@@ -58385,12 +58385,12 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
         <is>
-          <t>6E 329</t>
+          <t>AI 2955</t>
         </is>
       </c>
       <c r="J763" t="inlineStr">
@@ -58400,17 +58400,17 @@
       </c>
       <c r="K763" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="L763" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M763" t="n">
         <v>0</v>
       </c>
       <c r="N763" t="n">
-        <v>7593</v>
+        <v>8052</v>
       </c>
       <c r="O763" t="inlineStr">
         <is>
@@ -58461,32 +58461,32 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
         <is>
-          <t>AI 2441</t>
+          <t>6E 329</t>
         </is>
       </c>
       <c r="J764" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="K764" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="L764" t="n">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="M764" t="n">
         <v>0</v>
       </c>
       <c r="N764" t="n">
-        <v>7921</v>
+        <v>7593</v>
       </c>
       <c r="O764" t="inlineStr">
         <is>
@@ -58537,32 +58537,32 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
         <is>
-          <t>SG 476</t>
+          <t>AI 2441</t>
         </is>
       </c>
       <c r="J765" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="K765" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="L765" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="M765" t="n">
         <v>0</v>
       </c>
       <c r="N765" t="n">
-        <v>6775</v>
+        <v>7921</v>
       </c>
       <c r="O765" t="inlineStr">
         <is>
@@ -58613,32 +58613,32 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
         <is>
-          <t>AI 2977</t>
+          <t>SG 476</t>
         </is>
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K766" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="L766" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="M766" t="n">
         <v>0</v>
       </c>
       <c r="N766" t="n">
-        <v>8052</v>
+        <v>6775</v>
       </c>
       <c r="O766" t="inlineStr">
         <is>
@@ -58689,12 +58689,12 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
         <is>
-          <t>6E 354</t>
+          <t>AI 2977</t>
         </is>
       </c>
       <c r="J767" t="inlineStr">
@@ -58714,7 +58714,7 @@
         <v>0</v>
       </c>
       <c r="N767" t="n">
-        <v>7593</v>
+        <v>8052</v>
       </c>
       <c r="O767" t="inlineStr">
         <is>
@@ -58765,22 +58765,22 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
         <is>
-          <t>AI 2985</t>
+          <t>6E 354</t>
         </is>
       </c>
       <c r="J768" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>21:55</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="L768" t="n">
@@ -58790,7 +58790,7 @@
         <v>0</v>
       </c>
       <c r="N768" t="n">
-        <v>8052</v>
+        <v>7593</v>
       </c>
       <c r="O768" t="inlineStr">
         <is>
@@ -58841,22 +58841,22 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
         <is>
-          <t>QP 1826</t>
+          <t>AI 2985</t>
         </is>
       </c>
       <c r="J769" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="K769" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="L769" t="n">
@@ -58866,7 +58866,7 @@
         <v>0</v>
       </c>
       <c r="N769" t="n">
-        <v>7904</v>
+        <v>8052</v>
       </c>
       <c r="O769" t="inlineStr">
         <is>
@@ -58917,22 +58917,22 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
         <is>
-          <t>AI 2805</t>
+          <t>QP 1826</t>
         </is>
       </c>
       <c r="J770" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="K770" t="inlineStr">
         <is>
-          <t>22:25</t>
+          <t>22:20</t>
         </is>
       </c>
       <c r="L770" t="n">
@@ -58942,7 +58942,7 @@
         <v>0</v>
       </c>
       <c r="N770" t="n">
-        <v>8183</v>
+        <v>7904</v>
       </c>
       <c r="O770" t="inlineStr">
         <is>
@@ -58993,12 +58993,12 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
         <is>
-          <t>6E 303</t>
+          <t>AI 2805</t>
         </is>
       </c>
       <c r="J771" t="inlineStr">
@@ -59008,17 +59008,17 @@
       </c>
       <c r="K771" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="L771" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M771" t="n">
         <v>0</v>
       </c>
       <c r="N771" t="n">
-        <v>7593</v>
+        <v>8183</v>
       </c>
       <c r="O771" t="inlineStr">
         <is>
@@ -59069,32 +59069,32 @@
       </c>
       <c r="H772" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I772" t="inlineStr">
         <is>
-          <t>SG 162</t>
+          <t>6E 303</t>
         </is>
       </c>
       <c r="J772" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="K772" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="L772" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="M772" t="n">
         <v>0</v>
       </c>
       <c r="N772" t="n">
-        <v>7119</v>
+        <v>7593</v>
       </c>
       <c r="O772" t="inlineStr">
         <is>
@@ -59145,32 +59145,32 @@
       </c>
       <c r="H773" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I773" t="inlineStr">
         <is>
-          <t>AI 2957</t>
+          <t>SG 162</t>
         </is>
       </c>
       <c r="J773" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="K773" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="L773" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="M773" t="n">
         <v>0</v>
       </c>
       <c r="N773" t="n">
-        <v>7653</v>
+        <v>7119</v>
       </c>
       <c r="O773" t="inlineStr">
         <is>
@@ -59221,17 +59221,17 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
         <is>
-          <t>6E 853</t>
+          <t>AI 2957</t>
         </is>
       </c>
       <c r="J774" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="K774" t="inlineStr">
@@ -59240,13 +59240,13 @@
         </is>
       </c>
       <c r="L774" t="n">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="M774" t="n">
         <v>0</v>
       </c>
       <c r="N774" t="n">
-        <v>7225</v>
+        <v>7653</v>
       </c>
       <c r="O774" t="inlineStr">
         <is>
@@ -59297,32 +59297,32 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
         <is>
-          <t>AI 2981</t>
+          <t>6E 853</t>
         </is>
       </c>
       <c r="J775" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="K775" t="inlineStr">
         <is>
-          <t>23:20</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="L775" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M775" t="n">
         <v>0</v>
       </c>
       <c r="N775" t="n">
-        <v>7653</v>
+        <v>7225</v>
       </c>
       <c r="O775" t="inlineStr">
         <is>
@@ -59373,12 +59373,12 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
         <is>
-          <t>SG 800</t>
+          <t>AI 2981</t>
         </is>
       </c>
       <c r="J776" t="inlineStr">
@@ -59388,17 +59388,17 @@
       </c>
       <c r="K776" t="inlineStr">
         <is>
-          <t>23:10</t>
+          <t>23:20</t>
         </is>
       </c>
       <c r="L776" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="M776" t="n">
         <v>0</v>
       </c>
       <c r="N776" t="n">
-        <v>7499</v>
+        <v>7653</v>
       </c>
       <c r="O776" t="inlineStr">
         <is>
@@ -59449,32 +59449,32 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
         <is>
-          <t>AI 2433</t>
+          <t>SG 800</t>
         </is>
       </c>
       <c r="J777" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="K777" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:10</t>
         </is>
       </c>
       <c r="L777" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="M777" t="n">
         <v>0</v>
       </c>
       <c r="N777" t="n">
-        <v>7653</v>
+        <v>7499</v>
       </c>
       <c r="O777" t="inlineStr">
         <is>
@@ -59525,32 +59525,32 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
         <is>
-          <t>6E 395</t>
+          <t>AI 2433</t>
         </is>
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="L778" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M778" t="n">
         <v>0</v>
       </c>
       <c r="N778" t="n">
-        <v>7225</v>
+        <v>7653</v>
       </c>
       <c r="O778" t="inlineStr">
         <is>
@@ -59601,32 +59601,32 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
         <is>
-          <t>AI 2999</t>
+          <t>6E 395</t>
         </is>
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="K779" t="inlineStr">
         <is>
-          <t>00:25</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="L779" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M779" t="n">
         <v>0</v>
       </c>
       <c r="N779" t="n">
-        <v>7653</v>
+        <v>7225</v>
       </c>
       <c r="O779" t="inlineStr">
         <is>
@@ -59682,17 +59682,17 @@
       </c>
       <c r="I780" t="inlineStr">
         <is>
-          <t>AI 2437</t>
+          <t>AI 2999</t>
         </is>
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="K780" t="inlineStr">
         <is>
-          <t>00:55</t>
+          <t>00:25</t>
         </is>
       </c>
       <c r="L780" t="n">
@@ -59753,12 +59753,12 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>SpiceJet</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
         <is>
-          <t>SG 802</t>
+          <t>AI 2437</t>
         </is>
       </c>
       <c r="J781" t="inlineStr">
@@ -59768,17 +59768,17 @@
       </c>
       <c r="K781" t="inlineStr">
         <is>
-          <t>00:50</t>
+          <t>00:55</t>
         </is>
       </c>
       <c r="L781" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="M781" t="n">
         <v>0</v>
       </c>
       <c r="N781" t="n">
-        <v>6775</v>
+        <v>7653</v>
       </c>
       <c r="O781" t="inlineStr">
         <is>
@@ -59829,22 +59829,22 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>SpiceJet</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
         <is>
-          <t>6E 6114</t>
+          <t>SG 802</t>
         </is>
       </c>
       <c r="J782" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>00:50</t>
         </is>
       </c>
       <c r="L782" t="n">
@@ -59854,7 +59854,7 @@
         <v>0</v>
       </c>
       <c r="N782" t="n">
-        <v>7225</v>
+        <v>6775</v>
       </c>
       <c r="O782" t="inlineStr">
         <is>
@@ -59905,32 +59905,32 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
         <is>
-          <t>AI 2439</t>
+          <t>6E 6114</t>
         </is>
       </c>
       <c r="J783" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="K783" t="inlineStr">
         <is>
-          <t>01:25</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="L783" t="n">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M783" t="n">
         <v>0</v>
       </c>
       <c r="N783" t="n">
-        <v>7653</v>
+        <v>7225</v>
       </c>
       <c r="O783" t="inlineStr">
         <is>
@@ -59981,32 +59981,32 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
         <is>
-          <t>6E 322</t>
+          <t>AI 2439</t>
         </is>
       </c>
       <c r="J784" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="K784" t="inlineStr">
         <is>
-          <t>01:45</t>
+          <t>01:25</t>
         </is>
       </c>
       <c r="L784" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="M784" t="n">
         <v>0</v>
       </c>
       <c r="N784" t="n">
-        <v>6963</v>
+        <v>7653</v>
       </c>
       <c r="O784" t="inlineStr">
         <is>
@@ -60032,7 +60032,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>DEL-JAI</t>
+          <t>DEL-BOM</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
@@ -60042,47 +60042,47 @@
       </c>
       <c r="E785" t="inlineStr">
         <is>
-          <t>JAI</t>
+          <t>BOM</t>
         </is>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
         <is>
-          <t>AI 1767</t>
+          <t>6E 322</t>
         </is>
       </c>
       <c r="J785" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>01:45</t>
         </is>
       </c>
       <c r="L785" t="n">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="M785" t="n">
         <v>0</v>
       </c>
       <c r="N785" t="n">
-        <v>3220</v>
+        <v>6963</v>
       </c>
       <c r="O785" t="inlineStr">
         <is>
@@ -60133,32 +60133,32 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="J786" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="K786" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="L786" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M786" t="n">
         <v>0</v>
       </c>
       <c r="N786" t="n">
-        <v>3010</v>
+        <v>3220</v>
       </c>
       <c r="O786" t="inlineStr">
         <is>
@@ -60209,29 +60209,32 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I787" t="inlineStr">
         <is>
-          <t>9I 805</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="K787" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="L787" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M787" t="n">
         <v>0</v>
+      </c>
+      <c r="N787" t="n">
+        <v>3010</v>
       </c>
       <c r="O787" t="inlineStr">
         <is>
@@ -60282,32 +60285,29 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
         <is>
-          <t>AI 429</t>
+          <t>9I 805</t>
         </is>
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="K788" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="L788" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M788" t="n">
         <v>0</v>
-      </c>
-      <c r="N788" t="n">
-        <v>3010</v>
       </c>
       <c r="O788" t="inlineStr">
         <is>
@@ -60358,32 +60358,32 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
         <is>
-          <t>6E 5033</t>
+          <t>AI 429</t>
         </is>
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="K789" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="L789" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M789" t="n">
         <v>0</v>
       </c>
       <c r="N789" t="n">
-        <v>5845</v>
+        <v>3010</v>
       </c>
       <c r="O789" t="inlineStr">
         <is>
@@ -60439,27 +60439,27 @@
       </c>
       <c r="I790" t="inlineStr">
         <is>
-          <t>6E 6131</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="J790" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="K790" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="L790" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M790" t="n">
         <v>0</v>
       </c>
       <c r="N790" t="n">
-        <v>4795</v>
+        <v>5845</v>
       </c>
       <c r="O790" t="inlineStr">
         <is>
@@ -60500,42 +60500,42 @@
       </c>
       <c r="F791" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G791" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
         <is>
-          <t>AI 1767</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="J791" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="K791" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="L791" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M791" t="n">
         <v>0</v>
       </c>
       <c r="N791" t="n">
-        <v>3220</v>
+        <v>4795</v>
       </c>
       <c r="O791" t="inlineStr">
         <is>
@@ -60586,32 +60586,32 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
         <is>
-          <t>6E 6190</t>
+          <t>AI 1767</t>
         </is>
       </c>
       <c r="J792" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="K792" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="L792" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M792" t="n">
         <v>0</v>
       </c>
       <c r="N792" t="n">
-        <v>3010</v>
+        <v>3220</v>
       </c>
       <c r="O792" t="inlineStr">
         <is>
@@ -60662,29 +60662,32 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Alliance Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
         <is>
-          <t>9I 805</t>
+          <t>6E 6190</t>
         </is>
       </c>
       <c r="J793" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="K793" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="L793" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M793" t="n">
         <v>0</v>
+      </c>
+      <c r="N793" t="n">
+        <v>3010</v>
       </c>
       <c r="O793" t="inlineStr">
         <is>
@@ -60735,32 +60738,29 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Air India</t>
+          <t>Alliance Air</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
         <is>
-          <t>AI 429</t>
+          <t>9I 805</t>
         </is>
       </c>
       <c r="J794" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="K794" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="L794" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="M794" t="n">
         <v>0</v>
-      </c>
-      <c r="N794" t="n">
-        <v>3010</v>
       </c>
       <c r="O794" t="inlineStr">
         <is>
@@ -60811,32 +60811,32 @@
       </c>
       <c r="H795" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India</t>
         </is>
       </c>
       <c r="I795" t="inlineStr">
         <is>
-          <t>6E 5033</t>
+          <t>AI 429</t>
         </is>
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="K795" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="L795" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M795" t="n">
         <v>0</v>
       </c>
       <c r="N795" t="n">
-        <v>3220</v>
+        <v>3010</v>
       </c>
       <c r="O795" t="inlineStr">
         <is>
@@ -60892,27 +60892,27 @@
       </c>
       <c r="I796" t="inlineStr">
         <is>
-          <t>6E 6131</t>
+          <t>6E 5033</t>
         </is>
       </c>
       <c r="J796" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="K796" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="L796" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="M796" t="n">
         <v>0</v>
       </c>
       <c r="N796" t="n">
-        <v>3010</v>
+        <v>3220</v>
       </c>
       <c r="O796" t="inlineStr">
         <is>
@@ -60938,57 +60938,57 @@
       </c>
       <c r="C797" t="inlineStr">
         <is>
-          <t>PNQ-BLR</t>
+          <t>DEL-JAI</t>
         </is>
       </c>
       <c r="D797" t="inlineStr">
         <is>
-          <t>PNQ</t>
+          <t>DEL</t>
         </is>
       </c>
       <c r="E797" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>JAI</t>
         </is>
       </c>
       <c r="F797" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G797" t="inlineStr">
         <is>
-          <t>+1wk</t>
+          <t>+3wk</t>
         </is>
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
         <is>
-          <t>IX 2681</t>
+          <t>6E 6131</t>
         </is>
       </c>
       <c r="J797" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="K797" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="L797" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="M797" t="n">
         <v>0</v>
       </c>
       <c r="N797" t="n">
-        <v>5536</v>
+        <v>3010</v>
       </c>
       <c r="O797" t="inlineStr">
         <is>
@@ -61039,32 +61039,32 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
         <is>
-          <t>6E 361</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="J798" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="K798" t="inlineStr">
         <is>
-          <t>02:55</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="L798" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M798" t="n">
         <v>0</v>
       </c>
       <c r="N798" t="n">
-        <v>5313</v>
+        <v>5536</v>
       </c>
       <c r="O798" t="inlineStr">
         <is>
@@ -61120,17 +61120,17 @@
       </c>
       <c r="I799" t="inlineStr">
         <is>
-          <t>6E 6564</t>
+          <t>6E 361</t>
         </is>
       </c>
       <c r="J799" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="K799" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>02:55</t>
         </is>
       </c>
       <c r="L799" t="n">
@@ -61196,21 +61196,21 @@
       </c>
       <c r="I800" t="inlineStr">
         <is>
-          <t>6E 6877</t>
+          <t>6E 6564</t>
         </is>
       </c>
       <c r="J800" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="K800" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="L800" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M800" t="n">
         <v>0</v>
@@ -61267,32 +61267,32 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
         <is>
-          <t>IX 2706</t>
+          <t>6E 6877</t>
         </is>
       </c>
       <c r="J801" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="K801" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="L801" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="M801" t="n">
         <v>0</v>
       </c>
       <c r="N801" t="n">
-        <v>5536</v>
+        <v>5313</v>
       </c>
       <c r="O801" t="inlineStr">
         <is>
@@ -61343,32 +61343,32 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
         <is>
-          <t>6E 391</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="J802" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="K802" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="L802" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M802" t="n">
         <v>0</v>
       </c>
       <c r="N802" t="n">
-        <v>5313</v>
+        <v>5536</v>
       </c>
       <c r="O802" t="inlineStr">
         <is>
@@ -61419,32 +61419,32 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
         <is>
-          <t>QP 1312</t>
+          <t>6E 391</t>
         </is>
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="K803" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="L803" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M803" t="n">
         <v>0</v>
       </c>
       <c r="N803" t="n">
-        <v>6005</v>
+        <v>5313</v>
       </c>
       <c r="O803" t="inlineStr">
         <is>
@@ -61500,17 +61500,17 @@
       </c>
       <c r="I804" t="inlineStr">
         <is>
-          <t>QP 1314</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="J804" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="K804" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="L804" t="n">
@@ -61520,7 +61520,7 @@
         <v>0</v>
       </c>
       <c r="N804" t="n">
-        <v>7951</v>
+        <v>6005</v>
       </c>
       <c r="O804" t="inlineStr">
         <is>
@@ -61576,27 +61576,27 @@
       </c>
       <c r="I805" t="inlineStr">
         <is>
-          <t>QP 1326</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="J805" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="K805" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="L805" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M805" t="n">
         <v>0</v>
       </c>
       <c r="N805" t="n">
-        <v>9549</v>
+        <v>7951</v>
       </c>
       <c r="O805" t="inlineStr">
         <is>
@@ -61647,32 +61647,32 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
         <is>
-          <t>6E 302</t>
+          <t>QP 1326</t>
         </is>
       </c>
       <c r="J806" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K806" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="L806" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M806" t="n">
         <v>0</v>
       </c>
       <c r="N806" t="n">
-        <v>11268</v>
+        <v>9549</v>
       </c>
       <c r="O806" t="inlineStr">
         <is>
@@ -61723,32 +61723,32 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
         <is>
-          <t>IX 2718</t>
+          <t>6E 302</t>
         </is>
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="K807" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="L807" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M807" t="n">
         <v>0</v>
       </c>
       <c r="N807" t="n">
-        <v>10834</v>
+        <v>11268</v>
       </c>
       <c r="O807" t="inlineStr">
         <is>
@@ -61799,32 +61799,32 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
         <is>
-          <t>6E 137</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="J808" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="L808" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M808" t="n">
         <v>0</v>
       </c>
       <c r="N808" t="n">
-        <v>8189</v>
+        <v>10834</v>
       </c>
       <c r="O808" t="inlineStr">
         <is>
@@ -61875,32 +61875,32 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
         <is>
-          <t>QP 1316</t>
+          <t>6E 137</t>
         </is>
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="L809" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M809" t="n">
         <v>0</v>
       </c>
       <c r="N809" t="n">
-        <v>9912</v>
+        <v>8189</v>
       </c>
       <c r="O809" t="inlineStr">
         <is>
@@ -61951,22 +61951,22 @@
       </c>
       <c r="H810" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I810" t="inlineStr">
         <is>
-          <t>6E 174</t>
+          <t>QP 1316</t>
         </is>
       </c>
       <c r="J810" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="K810" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="L810" t="n">
@@ -61976,7 +61976,7 @@
         <v>0</v>
       </c>
       <c r="N810" t="n">
-        <v>8189</v>
+        <v>9912</v>
       </c>
       <c r="O810" t="inlineStr">
         <is>
@@ -62027,32 +62027,32 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
         <is>
-          <t>IX 2874</t>
+          <t>6E 174</t>
         </is>
       </c>
       <c r="J811" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="L811" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M811" t="n">
         <v>0</v>
       </c>
       <c r="N811" t="n">
-        <v>8047</v>
+        <v>8189</v>
       </c>
       <c r="O811" t="inlineStr">
         <is>
@@ -62103,32 +62103,32 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
         <is>
-          <t>6E 107</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="L812" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M812" t="n">
         <v>0</v>
       </c>
       <c r="N812" t="n">
-        <v>5313</v>
+        <v>8047</v>
       </c>
       <c r="O812" t="inlineStr">
         <is>
@@ -62179,32 +62179,32 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
         <is>
-          <t>IX 2839</t>
+          <t>6E 107</t>
         </is>
       </c>
       <c r="J813" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="K813" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="L813" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M813" t="n">
         <v>0</v>
       </c>
       <c r="N813" t="n">
-        <v>5536</v>
+        <v>5313</v>
       </c>
       <c r="O813" t="inlineStr">
         <is>
@@ -62255,22 +62255,22 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
         <is>
-          <t>QP 1318</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="K814" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="L814" t="n">
@@ -62280,7 +62280,7 @@
         <v>0</v>
       </c>
       <c r="N814" t="n">
-        <v>5613</v>
+        <v>5536</v>
       </c>
       <c r="O814" t="inlineStr">
         <is>
@@ -62331,32 +62331,32 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
         <is>
-          <t>6E 6055</t>
+          <t>QP 1318</t>
         </is>
       </c>
       <c r="J815" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="K815" t="inlineStr">
         <is>
-          <t>01:30</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="L815" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M815" t="n">
         <v>0</v>
       </c>
       <c r="N815" t="n">
-        <v>5313</v>
+        <v>5613</v>
       </c>
       <c r="O815" t="inlineStr">
         <is>
@@ -62397,42 +62397,42 @@
       </c>
       <c r="F816" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G816" t="inlineStr">
         <is>
-          <t>+3wk</t>
+          <t>+1wk</t>
         </is>
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
         <is>
-          <t>IX 2681</t>
+          <t>6E 6055</t>
         </is>
       </c>
       <c r="J816" t="inlineStr">
         <is>
-          <t>00:05</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="K816" t="inlineStr">
         <is>
-          <t>01:40</t>
+          <t>01:30</t>
         </is>
       </c>
       <c r="L816" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M816" t="n">
         <v>0</v>
       </c>
       <c r="N816" t="n">
-        <v>5536</v>
+        <v>5313</v>
       </c>
       <c r="O816" t="inlineStr">
         <is>
@@ -62483,32 +62483,32 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
         <is>
-          <t>6E 361</t>
+          <t>IX 2681</t>
         </is>
       </c>
       <c r="J817" t="inlineStr">
         <is>
-          <t>01:15</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>02:55</t>
+          <t>01:40</t>
         </is>
       </c>
       <c r="L817" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M817" t="n">
         <v>0</v>
       </c>
       <c r="N817" t="n">
-        <v>5313</v>
+        <v>5536</v>
       </c>
       <c r="O817" t="inlineStr">
         <is>
@@ -62564,17 +62564,17 @@
       </c>
       <c r="I818" t="inlineStr">
         <is>
-          <t>6E 6564</t>
+          <t>6E 361</t>
         </is>
       </c>
       <c r="J818" t="inlineStr">
         <is>
-          <t>03:15</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="K818" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>02:55</t>
         </is>
       </c>
       <c r="L818" t="n">
@@ -62640,21 +62640,21 @@
       </c>
       <c r="I819" t="inlineStr">
         <is>
-          <t>6E 6877</t>
+          <t>6E 6564</t>
         </is>
       </c>
       <c r="J819" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>03:15</t>
         </is>
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="L819" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M819" t="n">
         <v>0</v>
@@ -62711,32 +62711,32 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
         <is>
-          <t>IX 2706</t>
+          <t>6E 6877</t>
         </is>
       </c>
       <c r="J820" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="K820" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="L820" t="n">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="M820" t="n">
         <v>0</v>
       </c>
       <c r="N820" t="n">
-        <v>5536</v>
+        <v>5313</v>
       </c>
       <c r="O820" t="inlineStr">
         <is>
@@ -62787,32 +62787,32 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
         <is>
-          <t>6E 391</t>
+          <t>IX 2706</t>
         </is>
       </c>
       <c r="J821" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="K821" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="L821" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M821" t="n">
         <v>0</v>
       </c>
       <c r="N821" t="n">
-        <v>5313</v>
+        <v>5536</v>
       </c>
       <c r="O821" t="inlineStr">
         <is>
@@ -62863,32 +62863,32 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
         <is>
-          <t>QP 1312</t>
+          <t>6E 391</t>
         </is>
       </c>
       <c r="J822" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="K822" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="L822" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="M822" t="n">
         <v>0</v>
       </c>
       <c r="N822" t="n">
-        <v>5428</v>
+        <v>5313</v>
       </c>
       <c r="O822" t="inlineStr">
         <is>
@@ -62944,17 +62944,17 @@
       </c>
       <c r="I823" t="inlineStr">
         <is>
-          <t>QP 1314</t>
+          <t>QP 1312</t>
         </is>
       </c>
       <c r="J823" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="K823" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="L823" t="n">
@@ -62964,7 +62964,7 @@
         <v>0</v>
       </c>
       <c r="N823" t="n">
-        <v>6660</v>
+        <v>5428</v>
       </c>
       <c r="O823" t="inlineStr">
         <is>
@@ -63020,27 +63020,27 @@
       </c>
       <c r="I824" t="inlineStr">
         <is>
-          <t>QP 1326</t>
+          <t>QP 1314</t>
         </is>
       </c>
       <c r="J824" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="K824" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="L824" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M824" t="n">
         <v>0</v>
       </c>
       <c r="N824" t="n">
-        <v>6214</v>
+        <v>6660</v>
       </c>
       <c r="O824" t="inlineStr">
         <is>
@@ -63091,32 +63091,32 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
         <is>
-          <t>6E 302</t>
+          <t>QP 1326</t>
         </is>
       </c>
       <c r="J825" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="K825" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="L825" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M825" t="n">
         <v>0</v>
       </c>
       <c r="N825" t="n">
-        <v>6545</v>
+        <v>6214</v>
       </c>
       <c r="O825" t="inlineStr">
         <is>
@@ -63167,32 +63167,32 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
         <is>
-          <t>IX 2718</t>
+          <t>6E 302</t>
         </is>
       </c>
       <c r="J826" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="K826" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="L826" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M826" t="n">
         <v>0</v>
       </c>
       <c r="N826" t="n">
-        <v>6386</v>
+        <v>6545</v>
       </c>
       <c r="O826" t="inlineStr">
         <is>
@@ -63243,32 +63243,32 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
         <is>
-          <t>6E 137</t>
+          <t>IX 2718</t>
         </is>
       </c>
       <c r="J827" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="K827" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="L827" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M827" t="n">
         <v>0</v>
       </c>
       <c r="N827" t="n">
-        <v>7587</v>
+        <v>6386</v>
       </c>
       <c r="O827" t="inlineStr">
         <is>
@@ -63319,32 +63319,32 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
         <is>
-          <t>QP 1316</t>
+          <t>6E 137</t>
         </is>
       </c>
       <c r="J828" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="K828" t="inlineStr">
         <is>
-          <t>19:25</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="L828" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="M828" t="n">
         <v>0</v>
       </c>
       <c r="N828" t="n">
-        <v>6660</v>
+        <v>7587</v>
       </c>
       <c r="O828" t="inlineStr">
         <is>
@@ -63395,22 +63395,22 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Akasa Air</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
         <is>
-          <t>6E 174</t>
+          <t>QP 1316</t>
         </is>
       </c>
       <c r="J829" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="K829" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="L829" t="n">
@@ -63420,7 +63420,7 @@
         <v>0</v>
       </c>
       <c r="N829" t="n">
-        <v>6094</v>
+        <v>6660</v>
       </c>
       <c r="O829" t="inlineStr">
         <is>
@@ -63471,32 +63471,32 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
         <is>
-          <t>IX 2874</t>
+          <t>6E 174</t>
         </is>
       </c>
       <c r="J830" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="K830" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="L830" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M830" t="n">
         <v>0</v>
       </c>
       <c r="N830" t="n">
-        <v>7555</v>
+        <v>6094</v>
       </c>
       <c r="O830" t="inlineStr">
         <is>
@@ -63547,32 +63547,32 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>IndiGo</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
         <is>
-          <t>6E 107</t>
+          <t>IX 2874</t>
         </is>
       </c>
       <c r="J831" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="K831" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="L831" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="M831" t="n">
         <v>0</v>
       </c>
       <c r="N831" t="n">
-        <v>6545</v>
+        <v>7555</v>
       </c>
       <c r="O831" t="inlineStr">
         <is>
@@ -63623,32 +63623,32 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>Air India Express</t>
+          <t>IndiGo</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
         <is>
-          <t>IX 2839</t>
+          <t>6E 107</t>
         </is>
       </c>
       <c r="J832" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="K832" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="L832" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M832" t="n">
         <v>0</v>
       </c>
       <c r="N832" t="n">
-        <v>7120</v>
+        <v>6545</v>
       </c>
       <c r="O832" t="inlineStr">
         <is>
@@ -63699,22 +63699,22 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t>Akasa Air</t>
+          <t>Air India Express</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
         <is>
-          <t>QP 1318</t>
+          <t>IX 2839</t>
         </is>
       </c>
       <c r="J833" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="K833" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="L833" t="n">
@@ -63724,7 +63724,7 @@
         <v>0</v>
       </c>
       <c r="N833" t="n">
-        <v>5804</v>
+        <v>7120</v>
       </c>
       <c r="O833" t="inlineStr">
         <is>
@@ -63775,39 +63775,115 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
+          <t>Akasa Air</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>QP 1318</t>
+        </is>
+      </c>
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>22:10</t>
+        </is>
+      </c>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>23:55</t>
+        </is>
+      </c>
+      <c r="L834" t="n">
+        <v>105</v>
+      </c>
+      <c r="M834" t="n">
+        <v>0</v>
+      </c>
+      <c r="N834" t="n">
+        <v>5804</v>
+      </c>
+      <c r="O834" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="P834" t="inlineStr">
+        <is>
+          <t>SerpAPI/Google Flights</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>2026-07-26T11:18:02</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>PNQ-BLR</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>PNQ</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>BLR</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>+3wk</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
           <t>IndiGo</t>
         </is>
       </c>
-      <c r="I834" t="inlineStr">
+      <c r="I835" t="inlineStr">
         <is>
           <t>6E 6055</t>
         </is>
       </c>
-      <c r="J834" t="inlineStr">
+      <c r="J835" t="inlineStr">
         <is>
           <t>23:50</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr">
+      <c r="K835" t="inlineStr">
         <is>
           <t>01:30</t>
         </is>
       </c>
-      <c r="L834" t="n">
+      <c r="L835" t="n">
         <v>100</v>
       </c>
-      <c r="M834" t="n">
-        <v>0</v>
-      </c>
-      <c r="N834" t="n">
+      <c r="M835" t="n">
+        <v>0</v>
+      </c>
+      <c r="N835" t="n">
         <v>5313</v>
       </c>
-      <c r="O834" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="P834" t="inlineStr">
+      <c r="O835" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="P835" t="inlineStr">
         <is>
           <t>SerpAPI/Google Flights</t>
         </is>
